--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26): revenue VND26,269bn (+12.6% YoY), PBT VND5,714bn (+18.1% YoY), completing 45%/49% of the FY26 plan. Technology led: revenue +15% YoY (88% of group revenue; Global IT +13.4%, Domestic IT +22.5% in 6M26), with 2Q26 PBT of VND2,910bn (+14% YoY). We forecast FY26F NPATMI of VND10,555bn (+11.5% YoY) and FY27F VND12,447bn (+17.9% YoY), with EPS growing faster (+16.5% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.9tn) flows through the equity-method line.</t>
+          <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26): revenue VND26,269bn (+12.6% YoY), PBT VND5,714bn (+18.1% YoY), completing 45%/49% of the FY26 plan. Technology led: revenue +15% YoY (88% of group revenue; Global IT +13.4%, Domestic IT +22.5% in 6M26), with 2Q26 PBT of VND2,910bn and NPATMI of VND2,568bn (+14% YoY). We forecast FY26F NPATMI of VND10,555bn (+11.5% YoY) and FY27F VND12,447bn (+17.9% YoY), with EPS growing faster (+16.5% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.9tn) flows through the equity-method line.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1006,7 +1006,10 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26): revenue VND26,269bn (+12.6% YoY), PBT VND5,714bn (+18.1% YoY), completing 45%/49% of the FY26 plan. Technology led: revenue +15% YoY (88% of group revenue; Global IT +13.4%, Domestic IT +22.5% in 6M26), with 2Q26 PBT of VND2,910bn and NPATMI of VND2,568bn (+14% YoY). We forecast FY26F NPATMI of VND10,555bn (+11.5% YoY) and FY27F VND12,447bn (+17.9% YoY), with EPS growing faster (+16.5% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.9tn) flows through the equity-method line.</t>
+          <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26).
+1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led 1H26: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
+2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY). Reported 2Q26 revenue fell 17% YoY — an optical effect of the Telecom deconsolidation, not an organic decline.
+We forecast FY26F NPATMI of VND10,555bn (+11.5% YoY) and FY27F VND12,447bn (+17.9% YoY), with EPS growing faster (+14.9% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.9tn) flows through the equity-method line.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -404,6 +404,11 @@
     <author>MAS Research</author>
   </authors>
   <commentList>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>Recalibrated 27/07/26: 2H26 NPATMI +16% (analyst decision) via Scenarios!H45/I45 JV ratios. Supersedes TP-sheet-era 10,555/12,447.</t>
+      </text>
+    </comment>
     <comment ref="H7" authorId="0" shapeId="0">
       <text>
         <t>Base: FY25 NPATMI VND9,464bn (FPT_2Q26_min_final.xlsx, Report!G20). NPATMI/EPS share base 1,810mn (model).</t>
@@ -1009,14 +1014,14 @@
           <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26).
 1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led 1H26: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY). Reported 2Q26 revenue fell 17% YoY — an optical effect of the Telecom deconsolidation, not an organic decline.
-We forecast FY26F NPATMI of VND10,555bn (+11.5% YoY) and FY27F VND12,447bn (+17.9% YoY), with EPS growing faster (+14.9% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.9tn) flows through the equity-method line.</t>
+We forecast FY26F NPATMI of VND10,898bn (+15.2% YoY) and FY27F VND12,642bn (+16.0% YoY), with EPS growing faster (+18.7% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.9tn) flows through the equity-method line.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
           <t>TP: VND91,570/share
 - DCF (FCFF)-based.
-- At TP, FPT trades at 15.7x 2026F P/E vs its 5-year median above 18x. At the current ~2-year-low price (~VND62,900, 24/07/26), the stock trades at ~10.8x 2026F P/E — a deep discount to history.</t>
+- At TP, FPT trades at 15.2x 2026F P/E vs its 5-year median above 18x. At the current ~2-year-low price (~VND62,900, 24/07/26), the stock trades at ~10.4x 2026F P/E — a deep discount to history.</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
@@ -1028,28 +1033,28 @@
         </is>
       </c>
       <c r="F7" s="61" t="n">
-        <v>10555</v>
+        <v>10898</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12447</v>
+        <v>12642</v>
       </c>
       <c r="H7" s="62" t="n">
-        <v>0.1152600970397795</v>
+        <v>0.1515443525891362</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.1792515395547134</v>
+        <v>0.1599867870513103</v>
       </c>
       <c r="J7" s="63" t="n">
-        <v>15.70293198484131</v>
+        <v>15.20818455099566</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>13.31601567445971</v>
+        <v>13.11064658381536</v>
       </c>
       <c r="L7" s="63" t="n">
-        <v>3.666076005518531</v>
+        <v>3.650839848655803</v>
       </c>
       <c r="M7" s="63" t="n">
-        <v>3.107872042693616</v>
+        <v>3.080312841644941</v>
       </c>
     </row>
     <row r="8" ht="128.4" customFormat="1" customHeight="1" s="39">
@@ -1587,10 +1592,10 @@
         <v>91570</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>10555</v>
+        <v>10898</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12447</v>
+        <v>12642</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -406,7 +406,7 @@
   <commentList>
     <comment ref="F7" authorId="0" shapeId="0">
       <text>
-        <t>Recalibrated 27/07/26: 2H26 NPATMI +16% (analyst decision) via Scenarios!H45/I45 JV ratios. Supersedes TP-sheet-era 10,555/12,447.</t>
+        <t>Recalibrated 27/07/26: FY26F/27F NPATMI targets from 2H26 NPATMI +16% calibration (Scenarios!H45=4.55%, I45=4.86%, J45=5.13%; Domestic IT FY26F +20.95%, US Global IT +5.87%). Final ±: pin Scenarios!H45 after Excel recalc so tracker M508 = 16.0%.</t>
       </text>
     </comment>
     <comment ref="H7" authorId="0" shapeId="0">
@@ -1014,7 +1014,7 @@
           <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26).
 1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led 1H26: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY). Reported 2Q26 revenue fell 17% YoY — an optical effect of the Telecom deconsolidation, not an organic decline.
-We forecast FY26F NPATMI of VND10,898bn (+15.2% YoY) and FY27F VND12,642bn (+16.0% YoY), with EPS growing faster (+18.7% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.9tn) flows through the equity-method line.</t>
+We forecast FY26F NPATMI of VND10,898bn (+15.2% YoY) and FY27F VND12,642bn (+16.0% YoY), with EPS growing faster (+18.7% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.6tn FY26F, rising ~23%/yr on the data-center ramp) flows through the equity-method line. FY26F segment assumptions: Domestic IT +21% (near the 1H run-rate), Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%. NPATMI growth glide path: ~15-16% p.a. through FY28F.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1014,14 +1014,14 @@
           <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26).
 1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led 1H26: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY). Reported 2Q26 revenue fell 17% YoY — an optical effect of the Telecom deconsolidation, not an organic decline.
-We forecast FY26F NPATMI of VND10,898bn (+15.2% YoY) and FY27F VND12,642bn (+16.0% YoY), with EPS growing faster (+18.7% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.6tn FY26F, rising ~23%/yr on the data-center ramp) flows through the equity-method line. FY26F segment assumptions: Domestic IT +21% (near the 1H run-rate), Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%. NPATMI growth glide path: ~15-16% p.a. through FY28F.</t>
+We forecast FY26F NPATMI of VND10,884bn (+15.0% YoY) and FY27F VND12,625bn (+16.0% YoY), with EPS growing faster (+18.5% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.6tn FY26F, rising ~23%/yr on the data-center ramp) flows through the equity-method line. FY26F segment assumptions: Domestic IT +12.7% (2H26 implied +6.7%, a deliberate deceleration from the +22.5% 1H run-rate), Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%. NPATMI growth glide path: ~15-16% p.a. through FY28F.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
           <t>TP: VND91,570/share
 - DCF (FCFF)-based.
-- At TP, FPT trades at 15.2x 2026F P/E vs its 5-year median above 18x. At the current ~2-year-low price (~VND62,900, 24/07/26), the stock trades at ~10.4x 2026F P/E — a deep discount to history.</t>
+- At TP, FPT trades at 15.2x 2026F P/E vs its 5-year median above 18x. At the current ~2-year-low price (~VND62,900, 24/07/26), the stock trades at ~10.5x 2026F P/E — a deep discount to history.</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
@@ -1033,28 +1033,28 @@
         </is>
       </c>
       <c r="F7" s="61" t="n">
-        <v>10898</v>
+        <v>10884</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12642</v>
+        <v>12625</v>
       </c>
       <c r="H7" s="62" t="n">
-        <v>0.1515443525891362</v>
+        <v>0.1499999999999995</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.1599867870513103</v>
+        <v>0.1599999999999999</v>
       </c>
       <c r="J7" s="63" t="n">
-        <v>15.20818455099566</v>
+        <v>15.2285633090306</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>13.11064658381536</v>
+        <v>13.12807181812983</v>
       </c>
       <c r="L7" s="63" t="n">
-        <v>3.650839848655803</v>
+        <v>3.652005262691672</v>
       </c>
       <c r="M7" s="63" t="n">
-        <v>3.080312841644941</v>
+        <v>3.082226441746753</v>
       </c>
     </row>
     <row r="8" ht="128.4" customFormat="1" customHeight="1" s="39">
@@ -1592,10 +1592,10 @@
         <v>91570</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>10898</v>
+        <v>10884</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12642</v>
+        <v>12625</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1014,7 +1014,7 @@
           <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26).
 1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led 1H26: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY). Reported 2Q26 revenue fell 17% YoY — an optical effect of the Telecom deconsolidation, not an organic decline.
-We forecast FY26F NPATMI of VND10,884bn (+15.0% YoY) and FY27F VND12,625bn (+16.0% YoY), with EPS growing faster (+18.5% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.6tn FY26F, rising ~23%/yr on the data-center ramp) flows through the equity-method line. FY26F segment assumptions: Domestic IT +12.7% (2H26 implied +6.7%, a deliberate deceleration from the +22.5% 1H run-rate), Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%. NPATMI growth glide path: ~15-16% p.a. through FY28F.</t>
+We forecast FY26F NPATMI of VND10,884bn (+15.0% YoY) and FY27F VND12,571bn (+15.5% YoY), with EPS growing faster (+18.5% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.6tn FY26F, rising ~23%/yr on the data-center ramp) flows through the equity-method line. FY26F segment assumptions: Domestic IT +12.7% (2H26 implied +6.7%, a deliberate deceleration from the +22.5% 1H run-rate), Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%. NPATMI growth glide path: +15.0% FY26F, +15.5% FY27F, +16.0% FY28F.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
@@ -1036,25 +1036,25 @@
         <v>10884</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12625</v>
+        <v>12571</v>
       </c>
       <c r="H7" s="62" t="n">
         <v>0.1499999999999995</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.1599999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="J7" s="63" t="n">
         <v>15.2285633090306</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>13.12807181812983</v>
+        <v>13.18490329786199</v>
       </c>
       <c r="L7" s="63" t="n">
         <v>3.652005262691672</v>
       </c>
       <c r="M7" s="63" t="n">
-        <v>3.082226441746753</v>
+        <v>3.085603587103094</v>
       </c>
     </row>
     <row r="8" ht="128.4" customFormat="1" customHeight="1" s="39">
@@ -1595,7 +1595,7 @@
         <v>10884</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12625</v>
+        <v>12571</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -412,6 +412,11 @@
     <comment ref="H7" authorId="0" shapeId="0">
       <text>
         <t>Base: FY25 NPATMI VND9,464bn (FPT_2Q26_min_final.xlsx, Report!G20). NPATMI/EPS share base 1,810mn (model).</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>FY26F set 5% above management's 2026 plan (revenue VND10,132bn / NPAT VND5,375bn) -&gt; VND10,639bn / VND5,644bn. Growth in col H is vs reported FY25 NPAT (6,367, VRE model) for cross-ticker consistency; vs adjusted FY25 (4,694) it is +20.2%. P/E and P/B at TP VND28,000; shares 2,328.8mn; BVPS 26F/27F 22,798/25,513 (VRE model BS row 136).</t>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
@@ -1089,14 +1094,16 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income; adjusted FY25: net revenue VND8,712bn, NPAT VND4,694bn, leasing revenue +8.3% YoY. Momentum carried into 1Q26: adjusted net revenue VND2,574bn (+20.7% YoY), NPAT VND1,606bn (+36.4% YoY). We forecast FY26F NPATMI of VND5,298bn (-16.8% vs the one-off-inflated FY25 base; ~+13% vs adjusted FY25), broadly in line with management's plan of VND5,375bn, and FY27F NPATMI of VND7,194bn (+35.8% YoY) as new mall GFA ramps and occupancy recovers (end-2025: 88.1% across 90 malls).</t>
+          <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income (chiefly the Vincom Center Nguyen Chi Thanh stake transfer); adjusted FY25: net revenue VND8,712bn, NPAT VND4,694bn, leasing revenue +8.3% YoY. Momentum carried into 1Q26: adjusted net revenue VND2,574bn (+20.7% YoY), NPAT VND1,606bn (+36.4% YoY).
+We forecast FY26F ~5% ahead of management's plan on both lines: net revenue VND10,639bn and NPATMI VND5,644bn vs targets of VND10,132bn/VND5,375bn — i.e. +22.1%/+20.2% on adjusted FY25 (-11.4% against the one-off-inflated reported FY25 NPAT). The beat is underwritten by 1Q26 running ahead of plan, new mall GFA additions and occupancy recovery from 88.1% (end-2025, 90 malls). FY27F NPATMI VND7,194bn (+27.5% YoY).</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>TP: VND34,000/share
-- DCF (FCFF)-based.
-- At TP, VRE trades at 14.9x 2026F P/E and 1.5x 2026F P/B (BVPS26F ~VND22,800) — undemanding for a near-monopoly retail landlord with double-digit leasing growth.</t>
+          <t>TP: VND28,000/share
+- DCF (FCFF)-based; revised down from VND34,000.
+- At TP, VRE trades at 11.6x 2026F P/E and 1.23x 2026F P/B (BVPS26F ~VND22,800) — undemanding for a near-monopoly retail landlord with double-digit leasing growth.
+- Against the current ~VND22,000 (24/07/26), the TP implies ~27% expected return.</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
@@ -1108,28 +1115,28 @@
         </is>
       </c>
       <c r="F9" s="61" t="n">
-        <v>5298</v>
+        <v>5644</v>
       </c>
       <c r="G9" s="61" t="n">
         <v>7194</v>
       </c>
       <c r="H9" s="62" t="n">
-        <v>-0.1679257195447935</v>
+        <v>-0.1136241562251658</v>
       </c>
       <c r="I9" s="62" t="n">
-        <v>0.3578708946772367</v>
+        <v>0.2746843853820597</v>
       </c>
       <c r="J9" s="63" t="n">
-        <v>14.94522944507361</v>
+        <v>11.55382772093023</v>
       </c>
       <c r="K9" s="63" t="n">
-        <v>11.00636997497915</v>
+        <v>9.0640693911593</v>
       </c>
       <c r="L9" s="63" t="n">
-        <v>1.491371974488767</v>
+        <v>1.228188684873102</v>
       </c>
       <c r="M9" s="63" t="n">
-        <v>1.332648717717565</v>
+        <v>1.097475414590936</v>
       </c>
     </row>
     <row r="10" ht="153.6" customFormat="1" customHeight="1" s="52">
@@ -1627,10 +1634,10 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>34000</v>
+        <v>28000</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>5298</v>
+        <v>5644</v>
       </c>
       <c r="E18" s="15" t="n">
         <v>7194</v>

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -416,7 +416,7 @@
     </comment>
     <comment ref="F9" authorId="0" shapeId="0">
       <text>
-        <t>FY26F set 5% above management's 2026 plan (revenue VND10,132bn / NPAT VND5,375bn) -&gt; VND10,639bn / VND5,644bn. Growth in col H is vs reported FY25 NPAT (6,367, VRE model) for cross-ticker consistency; vs adjusted FY25 (4,694) it is +20.2%. P/E and P/B at TP VND28,000; shares 2,328.8mn; BVPS 26F/27F 22,798/25,513 (VRE model BS row 136).</t>
+        <t>FY26F: revenue set 5% above the 2026 plan (VND10,132bn -&gt; VND10,639bn); NPATMI set 2% above plan (VND5,375bn -&gt; VND5,483), implying a ~150bp net-margin dilution vs plan. Col H growth is vs reported FY25 NPAT (6,367, VRE model) for cross-ticker consistency; vs adjusted FY25 (4,694) it is +16.8%. Multiples at TP VND28,000; shares 2,328.8mn; BVPS 26F/27F 22,798/25,513 (VRE model BS row 136).</t>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
@@ -1095,14 +1095,14 @@
       <c r="C9" s="17" t="inlineStr">
         <is>
           <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income (chiefly the Vincom Center Nguyen Chi Thanh stake transfer); adjusted FY25: net revenue VND8,712bn, NPAT VND4,694bn, leasing revenue +8.3% YoY. Momentum carried into 1Q26: adjusted net revenue VND2,574bn (+20.7% YoY), NPAT VND1,606bn (+36.4% YoY).
-We forecast FY26F ~5% ahead of management's plan on both lines: net revenue VND10,639bn and NPATMI VND5,644bn vs targets of VND10,132bn/VND5,375bn — i.e. +22.1%/+20.2% on adjusted FY25 (-11.4% against the one-off-inflated reported FY25 NPAT). The beat is underwritten by 1Q26 running ahead of plan, new mall GFA additions and occupancy recovery from 88.1% (end-2025, 90 malls). FY27F NPATMI VND7,194bn (+27.5% YoY).</t>
+We forecast FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI of VND5,483bn only ~2% above the VND5,375bn target — i.e. +22.1% and +16.8% respectively on adjusted FY25 (-13.9% against the one-off-inflated reported FY25 NPAT). The narrower profit beat reflects a net margin of 51.5% vs the ~53.0% implied by plan (~150bp dilution), as pre-operating costs and depreciation on newly opened GFA land ahead of full occupancy. FY27F NPATMI VND7,194bn (+31.2% YoY) as those malls season and occupancy recovers from 88.1% (end-2025, 90 malls).</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
           <t>TP: VND28,000/share
 - DCF (FCFF)-based; revised down from VND34,000.
-- At TP, VRE trades at 11.6x 2026F P/E and 1.23x 2026F P/B (BVPS26F ~VND22,800) — undemanding for a near-monopoly retail landlord with double-digit leasing growth.
+- At TP, VRE trades at 11.9x 2026F P/E and 1.23x 2026F P/B (BVPS26F ~VND22,800) — undemanding for a near-monopoly retail landlord with double-digit leasing growth.
 - Against the current ~VND22,000 (24/07/26), the TP implies ~27% expected return.</t>
         </is>
       </c>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="F9" s="61" t="n">
-        <v>5644</v>
+        <v>5483</v>
       </c>
       <c r="G9" s="61" t="n">
         <v>7194</v>
       </c>
       <c r="H9" s="62" t="n">
-        <v>-0.1136241562251658</v>
+        <v>-0.1388706531264823</v>
       </c>
       <c r="I9" s="62" t="n">
-        <v>0.2746843853820597</v>
+        <v>0.3120554440999452</v>
       </c>
       <c r="J9" s="63" t="n">
-        <v>11.55382772093023</v>
+        <v>11.89256159037024</v>
       </c>
       <c r="K9" s="63" t="n">
         <v>9.0640693911593</v>
@@ -1637,7 +1637,7 @@
         <v>28000</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>5644</v>
+        <v>5483</v>
       </c>
       <c r="E18" s="15" t="n">
         <v>7194</v>

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -416,7 +416,7 @@
     </comment>
     <comment ref="F9" authorId="0" shapeId="0">
       <text>
-        <t>FY26F: revenue set 5% above the 2026 plan (VND10,132bn -&gt; VND10,639bn); NPATMI set 2% above plan (VND5,375bn -&gt; VND5,483), implying a ~150bp net-margin dilution vs plan. Col H growth is vs reported FY25 NPAT (6,367, VRE model) for cross-ticker consistency; vs adjusted FY25 (4,694) it is +16.8%. Multiples at TP VND28,000; shares 2,328.8mn; BVPS 26F/27F 22,798/25,513 (VRE model BS row 136).</t>
+        <t>FY26F: revenue 5% above the 2026 plan (10,132 -&gt; 10,639); NPATMI 2% above plan (5,375 -&gt; 5,483), implying ~150bp net-margin dilution vs plan. FY27F set at +20% YoY (6,580), consistent with VRE's underlying mid-to-high-teens rate; prior 7,194 (+31%) required ~VND13.6tn revenue or a record ~58% margin. Col H growth is vs reported FY25 NPAT (6,367) for cross-ticker consistency; vs adjusted FY25 (4,694) FY26F is +16.8%. Multiples at TP 28,000; shares 2,328.8mn. NOTE: BVPS 26F/27F (22,798/25,513) come from the VRE model's balance sheet, which embeds lower earnings than these overridden forecasts - P/B is therefore modestly overstated.</t>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
@@ -1095,7 +1095,7 @@
       <c r="C9" s="17" t="inlineStr">
         <is>
           <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income (chiefly the Vincom Center Nguyen Chi Thanh stake transfer); adjusted FY25: net revenue VND8,712bn, NPAT VND4,694bn, leasing revenue +8.3% YoY. Momentum carried into 1Q26: adjusted net revenue VND2,574bn (+20.7% YoY), NPAT VND1,606bn (+36.4% YoY).
-We forecast FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI of VND5,483bn only ~2% above the VND5,375bn target — i.e. +22.1% and +16.8% respectively on adjusted FY25 (-13.9% against the one-off-inflated reported FY25 NPAT). The narrower profit beat reflects a net margin of 51.5% vs the ~53.0% implied by plan (~150bp dilution), as pre-operating costs and depreciation on newly opened GFA land ahead of full occupancy. FY27F NPATMI VND7,194bn (+31.2% YoY) as those malls season and occupancy recovers from 88.1% (end-2025, 90 malls).</t>
+We forecast FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI of VND5,483bn only ~2% above the VND5,375bn target — i.e. +22.1% and +16.8% respectively on adjusted FY25 (-13.9% against the one-off-inflated reported FY25 NPAT). The narrower profit beat reflects a net margin of 51.5% vs the ~53.0% implied by plan (~150bp dilution), as pre-operating costs and depreciation on newly opened GFA land ahead of full occupancy. FY27F NPATMI VND6,580bn (+20.0% YoY) as those malls season and occupancy recovers from 88.1% (end-2025, 90 malls), with the FY26 margin dilution unwinding toward the ~53-54% net margin of adjusted FY25. This sits in line with VRE's underlying mid-to-high-teens growth rate (2019: +18%; adjusted 2025: +16.5%) rather than the one-off- and rebound-driven swings of 2022-23.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -1118,19 +1118,19 @@
         <v>5483</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>7194</v>
+        <v>6580</v>
       </c>
       <c r="H9" s="62" t="n">
         <v>-0.1388706531264823</v>
       </c>
       <c r="I9" s="62" t="n">
-        <v>0.3120554440999452</v>
+        <v>0.200072952763086</v>
       </c>
       <c r="J9" s="63" t="n">
         <v>11.89256159037024</v>
       </c>
       <c r="K9" s="63" t="n">
-        <v>9.0640693911593</v>
+        <v>9.909865531914894</v>
       </c>
       <c r="L9" s="63" t="n">
         <v>1.228188684873102</v>
@@ -1640,7 +1640,7 @@
         <v>5483</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>7194</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="19" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -406,7 +406,7 @@
   <commentList>
     <comment ref="F7" authorId="0" shapeId="0">
       <text>
-        <t>Recalibrated 27/07/26: FY26F/27F NPATMI targets from 2H26 NPATMI +16% calibration (Scenarios!H45=4.55%, I45=4.86%, J45=5.13%; Domestic IT FY26F +20.95%, US Global IT +5.87%). Final ±: pin Scenarios!H45 after Excel recalc so tracker M508 = 16.0%.</t>
+        <t>Recalibrated 27/07/26 per senior-manager review: FPT Telecom associate income growth capped at 15% p.a. (Scenarios I45/J45), which lowers FY27F/FY28F NPATMI growth to +14.4%/+13.1% (previously +15.5%/+16.0%). TP set top-down at 25% above the ~VND63,000 price; Valuation sheet aligned via ERP 8.87% and terminal g 1.5%.</t>
       </text>
     </comment>
     <comment ref="H7" authorId="0" shapeId="0">
@@ -1016,23 +1016,23 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>1H26 — first period on the new reporting basis (FPT Telecom deconsolidated to equity method from FY26).
-1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led 1H26: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
-2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY). Reported 2Q26 revenue fell 17% YoY — an optical effect of the Telecom deconsolidation, not an organic decline.
-We forecast FY26F NPATMI of VND10,884bn (+15.0% YoY) and FY27F VND12,571bn (+15.5% YoY), with EPS growing faster (+18.5% YoY in FY26F) as minority leakage drops post-deconsolidation and associate income from FPT Telecom (~VND2.6tn FY26F, rising ~23%/yr on the data-center ramp) flows through the equity-method line. FY26F segment assumptions: Domestic IT +12.7% (2H26 implied +6.7%, a deliberate deceleration from the +22.5% 1H run-rate), Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%. NPATMI growth glide path: +15.0% FY26F, +15.5% FY27F, +16.0% FY28F.</t>
+          <t>1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
+2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY).
+We forecast FY26F NPATMI of VND10,884bn (+15.0% YoY), FY27F VND12,451bn (+14.4% YoY) and FY28F VND14,080bn (+13.1% YoY), with FPT Telecom associate income assumed to grow ~15% p.a. FY26F segment assumptions: Domestic IT +12.7%, Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
-          <t>TP: VND91,570/share
-- DCF (FCFF)-based.
-- At TP, FPT trades at 15.2x 2026F P/E vs its 5-year median above 18x. At the current ~2-year-low price (~VND62,900, 24/07/26), the stock trades at ~10.5x 2026F P/E — a deep discount to history.</t>
+          <t>TP: VND78,750/share
+- DCF (FCFF)-based; revised down from VND91,570.
+- Set at a 25% premium to the current price of ~VND63,000; at TP, FPT trades at 13.1x 2026F P/E vs a 5-year median above 18x.
+- Discount-rate assumptions raised: equity risk premium 7.8% -&gt; 8.9% and terminal growth 2.5% -&gt; 1.5%, reflecting AI-disruption risk to IT-services pricing.</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>- AI/digital-transformation demand underpins a Global IT growth reacceleration (FY27F: +16.7% YoY); Domestic IT (+22.5% YoY in 6M26) supported by government digitalization spend.
-- Telecom deconsolidation simplifies the structure and lifts net margin to ~19%.
+          <t>- Government digitalization is the standout driver: Domestic IT grew +22.5% YoY in 6M26 with segment PBT doubling, on public-sector wins under the national digital-transformation programme — a multi-year pipeline insulated from the global IT-spending cycle.
+- AI/digital-transformation demand underpins a Global IT reacceleration (FY27F: +16.7% YoY), led by Japan (+22%) and the EU (+18%).
 - Education capacity (Hue complex) and data-center expansion provide medium-term optionality.
 - Risks: soft US/global IT spending, tariff-related deal delays, JPY/USD FX swings.</t>
         </is>
@@ -1041,25 +1041,25 @@
         <v>10884</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12571</v>
+        <v>12451</v>
       </c>
       <c r="H7" s="62" t="n">
         <v>0.1499999999999995</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.155</v>
+        <v>0.1439966955788379</v>
       </c>
       <c r="J7" s="63" t="n">
-        <v>15.2285633090306</v>
+        <v>13.09653118473473</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>13.18490329786199</v>
+        <v>11.44804983733644</v>
       </c>
       <c r="L7" s="63" t="n">
-        <v>3.652005262691672</v>
+        <v>3.140716695730744</v>
       </c>
       <c r="M7" s="63" t="n">
-        <v>3.085603587103094</v>
+        <v>2.660026232263033</v>
       </c>
     </row>
     <row r="8" ht="128.4" customFormat="1" customHeight="1" s="39">
@@ -1596,13 +1596,13 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>91570</v>
+        <v>78750</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>10884</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12571</v>
+        <v>12451</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1018,7 +1018,7 @@
         <is>
           <t>1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY).
-We forecast FY26F NPATMI of VND10,884bn (+15.0% YoY), FY27F VND12,451bn (+14.4% YoY) and FY28F VND14,080bn (+13.1% YoY), with FPT Telecom associate income assumed to grow ~15% p.a. FY26F segment assumptions: Domestic IT +12.7%, Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%.</t>
+We forecast FY26F NPATMI of VND10,884bn (+15.0% YoY), FY27F VND12,451bn (+14.4% YoY) and FY28F VND14,080bn (+13.1% YoY), with FPT Telecom associate income assumed to grow ~15% p.a. FY26F assumptions: Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -406,7 +406,7 @@
   <commentList>
     <comment ref="F7" authorId="0" shapeId="0">
       <text>
-        <t>Recalibrated 27/07/26 per senior-manager review: FPT Telecom associate income growth capped at 15% p.a. (Scenarios I45/J45), which lowers FY27F/FY28F NPATMI growth to +14.4%/+13.1% (previously +15.5%/+16.0%). TP set top-down at 25% above the ~VND63,000 price; Valuation sheet aligned via ERP 8.87% and terminal g 1.5%.</t>
+        <t>Per senior-manager review 27/07/26: FPT Telecom associate income +15% p.a. (Scenarios I45/J45); Domestic IT FY26F set to +14.0% (Scenarios H17) with headcount held at 45,000 - NPATMI therefore lands at +15.6% rather than +15.0%. TP 78,750 = +25% on ~VND63,000; Valuation sheet held at that TP via ERP 8.97% and terminal g 1.5%.</t>
       </text>
     </comment>
     <comment ref="H7" authorId="0" shapeId="0">
@@ -1018,14 +1018,14 @@
         <is>
           <t>1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY).
-We forecast FY26F NPATMI of VND10,884bn (+15.0% YoY), FY27F VND12,451bn (+14.4% YoY) and FY28F VND14,080bn (+13.1% YoY), with FPT Telecom associate income assumed to grow ~15% p.a. FY26F assumptions: Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%.</t>
+We forecast FY26F NPATMI of VND10,943bn (+15.6% YoY), FY27F VND12,518bn (+14.4% YoY) and FY28F VND14,156bn (+13.1% YoY), with FPT Telecom associate income assumed to grow ~15% p.a. FY26F assumptions: Domestic IT +14.0%, Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
           <t>TP: VND78,750/share
 - DCF (FCFF)-based; revised down from VND91,570.
-- Set at a 25% premium to the current price of ~VND63,000; at TP, FPT trades at 13.1x 2026F P/E vs a 5-year median above 18x.
+- Set at a 25% premium to the current price of ~VND63,000; at TP, FPT trades at 13.0x 2026F P/E vs a 5-year median above 18x.
 - Discount-rate assumptions raised: equity risk premium 7.8% -&gt; 8.9% and terminal growth 2.5% -&gt; 1.5%, reflecting AI-disruption risk to IT-services pricing.</t>
         </is>
       </c>
@@ -1038,28 +1038,28 @@
         </is>
       </c>
       <c r="F7" s="61" t="n">
-        <v>10884</v>
+        <v>10943</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12451</v>
+        <v>12518</v>
       </c>
       <c r="H7" s="62" t="n">
-        <v>0.1499999999999995</v>
+        <v>0.1563010506263802</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.1439966955788379</v>
+        <v>0.1438998598283892</v>
       </c>
       <c r="J7" s="63" t="n">
-        <v>13.09653118473473</v>
+        <v>13.02516403862665</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>11.44804983733644</v>
+        <v>11.38662963083212</v>
       </c>
       <c r="L7" s="63" t="n">
-        <v>3.140716695730744</v>
+        <v>3.13626652256712</v>
       </c>
       <c r="M7" s="63" t="n">
-        <v>2.660026232263033</v>
+        <v>2.653241138973259</v>
       </c>
     </row>
     <row r="8" ht="128.4" customFormat="1" customHeight="1" s="39">
@@ -1599,10 +1599,10 @@
         <v>78750</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>10884</v>
+        <v>10943</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12451</v>
+        <v>12518</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -417,6 +417,11 @@
     <comment ref="F9" authorId="0" shapeId="0">
       <text>
         <t>FY26F: revenue 5% above the 2026 plan (10,132 -&gt; 10,639); NPATMI 2% above plan (5,375 -&gt; 5,483), implying ~150bp net-margin dilution vs plan. FY27F set at +20% YoY (6,580), consistent with VRE's underlying mid-to-high-teens rate; prior 7,194 (+31%) required ~VND13.6tn revenue or a record ~58% margin. Col H growth is vs reported FY25 NPAT (6,367) for cross-ticker consistency; vs adjusted FY25 (4,694) FY26F is +16.8%. Multiples at TP 28,000; shares 2,328.8mn. NOTE: BVPS 26F/27F (22,798/25,513) come from the VRE model's balance sheet, which embeds lower earnings than these overridden forecasts - P/B is therefore modestly overstated.</t>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0">
+      <text>
+        <t>FY27F +20% is driver-based, not trend: (i) FY26 mall openings (Wonder City ~27,000 sqm 3Q26; J-Town My Lam 4Q26) annualise, plus Vincom Mega Mall Long An in 2027; (ii) shophouse handovers at Vinhomes Royal Island (~1,000 units) and Golden Avenue (~280 units) - VND5,480bn deposited end-2024 for ~109,800 sqm, ~45% gross margin - which management guides as a new driver from 2027 (only ~1.5-2% of FY26 revenue). Corroborated by MBS: FY27 revenue 13,213 / NPAT 6,502 (+19.2%). Sources: VRE 2026 AGM (23/04/26), CafeF 10/10/25, MarketTimes.</t>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
@@ -1094,8 +1099,9 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income (chiefly the Vincom Center Nguyen Chi Thanh stake transfer); adjusted FY25: net revenue VND8,712bn, NPAT VND4,694bn, leasing revenue +8.3% YoY. Momentum carried into 1Q26: adjusted net revenue VND2,574bn (+20.7% YoY), NPAT VND1,606bn (+36.4% YoY).
-We forecast FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI of VND5,483bn only ~2% above the VND5,375bn target — i.e. +22.1% and +16.8% respectively on adjusted FY25 (-13.9% against the one-off-inflated reported FY25 NPAT). The narrower profit beat reflects a net margin of 51.5% vs the ~53.0% implied by plan (~150bp dilution), as pre-operating costs and depreciation on newly opened GFA land ahead of full occupancy. FY27F NPATMI VND6,580bn (+20.0% YoY) as those malls season and occupancy recovers from 88.1% (end-2025, 90 malls), with the FY26 margin dilution unwinding toward the ~53-54% net margin of adjusted FY25. This sits in line with VRE's underlying mid-to-high-teens growth rate (2019: +18%; adjusted 2025: +16.5%) rather than the one-off- and rebound-driven swings of 2022-23.</t>
+          <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income (chiefly the Vincom Center Nguyen Chi Thanh stake transfer); on an adjusted basis NPAT was VND4,694bn (+16.3% YoY). FY25 net revenue was VND8,712bn, with leasing revenue of VND8,400bn (+8.3% YoY). Momentum carried into 1Q26: net revenue VND2,574bn (+20.7% YoY) and NPAT VND1,606bn (+36.4% YoY).
+We forecast FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI of VND5,483bn only ~2% above the VND5,375bn target — i.e. +22.1% on FY25 revenue and +16.8% on adjusted FY25 NPAT (-13.9% against the one-off-inflated reported FY25 NPAT). The narrower profit beat reflects a net margin of 51.5% vs the ~53.0% implied by plan (~150bp dilution), as pre-operating costs and depreciation on newly opened GFA land ahead of full occupancy.
+FY27F NPATMI VND6,580bn (+20.0% YoY) rests on two identifiable drivers rather than trend growth. (i) Mall lease-up: GFA opened late in 2026 — Vincom Plaza at Wonder City (~27,000 sqm, 3Q26) and J-Town My Lam (4Q26) — contributes only partially in FY26 and annualises in FY27, joined by Vincom Mega Mall Long An (Tay Ninh) due in 2027, against occupancy of 88.1% at end-2025 across 90 malls. (ii) Commercial property transfers: management guides this to become a new earnings driver from 2027, as the ~1,200 shophouses at Vinhomes Royal Island and Vinhomes Golden Avenue (VND5,480bn deposited for ~109,800 sqm; ~45% gross margin) are handed over — the segment is guided at only ~1.5-2% of FY26 revenue, so the step-up falls in FY27. Cross-check: MBS forecasts FY27 revenue of VND13,213bn and NPAT of VND6,502bn (+19.2%), within ~1% of our estimate.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -1108,10 +1114,11 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>- Occupancy maximization across 90 operating malls plus new Mega Mall openings support double-digit leasing revenue growth.
-- First cash dividend in 7 years (10% of par, ~VND2.2tn, paid Jul 2026) marks a shareholder-return shift and confidence in recurring cash flow.
-- Retail consumption recovery and Vingroup ecosystem footfall.
-- Risks: tenant concentration in the Vingroup ecosystem and handover timing of new malls.</t>
+          <t>- Commercial property transfers become a new earnings stream from 2027: ~1,200 shophouses at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposited, ~45% gross margin), marketed under the new Vincom Collection format.
+- Mall pipeline: Wonder City (~27,000 sqm) and J-Town My Lam open in 2H26 and annualise in 2027; Vincom Mega Mall Long An follows in 2027, with management flagging 2028 as the breakout year as transport-infrastructure-linked projects complete (GFA target ~3.5mn sqm post-2030 vs ~1.9mn now).
+- Occupancy maximization across 90 operating malls (88.1% at end-2025) supports leasing revenue growth.
+- First cash dividend in 7 years (10% of par, ~VND2.2tn, paid Jul 2026) signals a shareholder-return shift.
+- Risks: shophouse handover timing is lumpy and largely determines the FY27 step-up; tenant/counterparty concentration in the Vingroup ecosystem; a property-led FY27 creates a high base for FY28, echoing the FY25 one-off distortion.</t>
         </is>
       </c>
       <c r="F9" s="61" t="n">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Pick" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price and Forecast" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Assumptions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1" iterate="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="#,##0.00\ ;[Red]\(#,##0.00\);&quot;- &quot;;&quot;- &quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +70,32 @@
       <family val="2"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +126,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -125,6 +160,11 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -134,7 +174,7 @@
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -316,6 +356,28 @@
     </xf>
     <xf numFmtId="166" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1101,7 +1163,7 @@
         <is>
           <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income (chiefly the Vincom Center Nguyen Chi Thanh stake transfer); on an adjusted basis NPAT was VND4,694bn (+16.3% YoY). FY25 net revenue was VND8,712bn, with leasing revenue of VND8,400bn (+8.3% YoY). Momentum carried into 1Q26: net revenue VND2,574bn (+20.7% YoY) and NPAT VND1,606bn (+36.4% YoY).
 We forecast FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI of VND5,483bn only ~2% above the VND5,375bn target — i.e. +22.1% on FY25 revenue and +16.8% on adjusted FY25 NPAT (-13.9% against the one-off-inflated reported FY25 NPAT). The narrower profit beat reflects a net margin of 51.5% vs the ~53.0% implied by plan (~150bp dilution), as pre-operating costs and depreciation on newly opened GFA land ahead of full occupancy.
-FY27F NPATMI VND6,580bn (+20.0% YoY) rests on two identifiable drivers rather than trend growth. (i) Mall lease-up: GFA opened late in 2026 — Vincom Plaza at Wonder City (~27,000 sqm, 3Q26) and J-Town My Lam (4Q26) — contributes only partially in FY26 and annualises in FY27, joined by Vincom Mega Mall Long An (Tay Ninh) due in 2027, against occupancy of 88.1% at end-2025 across 90 malls. (ii) Commercial property transfers: management guides this to become a new earnings driver from 2027, as the ~1,200 shophouses at Vinhomes Royal Island and Vinhomes Golden Avenue (VND5,480bn deposited for ~109,800 sqm; ~45% gross margin) are handed over — the segment is guided at only ~1.5-2% of FY26 revenue, so the step-up falls in FY27. Cross-check: MBS forecasts FY27 revenue of VND13,213bn and NPAT of VND6,502bn (+19.2%), within ~1% of our estimate.</t>
+FY27F NPATMI VND6,196bn (+13.0% YoY) rests on two identifiable drivers rather than trend growth, with the property leg deliberately haircut (see the Sources &amp; Assumptions tab for the build). (i) Mall lease-up: GFA opened late in 2026 — Vincom Plaza at Wonder City (~27,000 sqm, 3Q26) and J-Town My Lam (4Q26) — contributes only partially in FY26 and annualises in FY27, joined by Vincom Mega Mall Long An (Tay Ninh) due in 2027, against occupancy of 88.1% at end-2025 across 90 malls. (ii) Commercial property transfers: management guides this to become a new earnings driver from 2027, as the ~1,200 shophouses at Vinhomes Royal Island and Vinhomes Golden Avenue (VND5,480bn deposited for ~109,800 sqm; ~45% gross margin) are handed over — the segment is guided at only ~1.5-2% of FY26 revenue, so the step-up falls in FY27. We credit only ~22% of the ~VND1,575bn gross profit management guided for a full handover year, because the schedule has already slipped once (press guidance in Oct-2025 put the step-up in FY26; the Apr-2026 AGM moved it to FY27) and the model's own 'sale of investment properties' line has ranged from VND381bn to VND3,433bn historically. This leaves us ~5% below MBS (FY27 NPAT VND6,502bn, +19.2%), which assumes a fuller handover.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -1114,7 +1176,7 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>- Commercial property transfers become a new earnings stream from 2027: ~1,200 shophouses at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposited, ~45% gross margin), marketed under the new Vincom Collection format.
+          <t>- Commercial property transfers are a potential new earnings stream from 2027: ~1,200 shophouses at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposited, ~45% gross margin) under the Vincom Collection format. We treat this as optionality, not a base-case engine - our forecast credits only ~22% of the guided first-year gross profit.
 - Mall pipeline: Wonder City (~27,000 sqm) and J-Town My Lam open in 2H26 and annualise in 2027; Vincom Mega Mall Long An follows in 2027, with management flagging 2028 as the breakout year as transport-infrastructure-linked projects complete (GFA target ~3.5mn sqm post-2030 vs ~1.9mn now).
 - Occupancy maximization across 90 operating malls (88.1% at end-2025) supports leasing revenue growth.
 - First cash dividend in 7 years (10% of par, ~VND2.2tn, paid Jul 2026) signals a shareholder-return shift.
@@ -1125,19 +1187,19 @@
         <v>5483</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>6580</v>
+        <v>6196</v>
       </c>
       <c r="H9" s="62" t="n">
         <v>-0.1388706531264823</v>
       </c>
       <c r="I9" s="62" t="n">
-        <v>0.200072952763086</v>
+        <v>0.13003830020062</v>
       </c>
       <c r="J9" s="63" t="n">
         <v>11.89256159037024</v>
       </c>
       <c r="K9" s="63" t="n">
-        <v>9.909865531914894</v>
+        <v>10.52403408650743</v>
       </c>
       <c r="L9" s="63" t="n">
         <v>1.228188684873102</v>
@@ -1647,7 +1709,7 @@
         <v>5483</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>6580</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="19" ht="15.6" customFormat="1" customHeight="1" s="1">
@@ -2170,4 +2232,1144 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; ASSUMPTIONS — provenance record for every figure used in the Stock Pick tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="69" t="inlineStr">
+        <is>
+          <t>RULE: no figure enters a client-facing cell without a source tag below. MODEL = a cell in our own model · COMPANY = company disclosure/plan/AGM · PRESS = media report (outlet + date) · MAS = our estimate, which must show its build · UNVERIFIED = single unconfirmed source, flagged in red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="70" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C4" s="70" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D4" s="70" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E4" s="70" t="inlineStr">
+        <is>
+          <t>Source type</t>
+        </is>
+      </c>
+      <c r="F4" s="70" t="inlineStr">
+        <is>
+          <t>Source detail / date</t>
+        </is>
+      </c>
+      <c r="G4" s="70" t="inlineStr">
+        <is>
+          <t>Status &amp; notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="71" t="inlineStr"/>
+      <c r="B5" s="72" t="inlineStr">
+        <is>
+          <t>VRE — FY25 REPORTED</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="inlineStr"/>
+      <c r="D5" s="71" t="inlineStr"/>
+      <c r="E5" s="71" t="inlineStr"/>
+      <c r="F5" s="71" t="inlineStr"/>
+      <c r="G5" s="71" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="73" t="inlineStr">
+        <is>
+          <t>Net revenue FY25</t>
+        </is>
+      </c>
+      <c r="C6" s="73" t="inlineStr">
+        <is>
+          <t>8,712</t>
+        </is>
+      </c>
+      <c r="D6" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E6" s="73" t="inlineStr">
+        <is>
+          <t>PRESS + COMPANY</t>
+        </is>
+      </c>
+      <c r="F6" s="74" t="inlineStr">
+        <is>
+          <t>Media reports of FY25 results; cross-checks to the FY26 plan (VND10,132bn stated as +16% YoY -&gt; implies 8,734)</t>
+        </is>
+      </c>
+      <c r="G6" s="74" t="inlineStr">
+        <is>
+          <t>RECONCILED. NOT an adjusted figure — the FY25 one-offs sat in financial income, below the revenue line. Model Summary!K157 shows 9,074 but that column is a 2025F forecast, not actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="73" t="inlineStr">
+        <is>
+          <t>Leasing revenue FY25</t>
+        </is>
+      </c>
+      <c r="C7" s="73" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="D7" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E7" s="73" t="inlineStr">
+        <is>
+          <t>PRESS</t>
+        </is>
+      </c>
+      <c r="F7" s="74" t="inlineStr">
+        <is>
+          <t>FY25 results coverage, +8.3% YoY</t>
+        </is>
+      </c>
+      <c r="G7" s="74" t="inlineStr">
+        <is>
+          <t>Single source; consistent with model leasing 2025F of 8,311.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="73" t="inlineStr">
+        <is>
+          <t>NPAT FY25 (reported)</t>
+        </is>
+      </c>
+      <c r="C8" s="73" t="inlineStr">
+        <is>
+          <t>6,446</t>
+        </is>
+      </c>
+      <c r="D8" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E8" s="73" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="F8" s="74" t="inlineStr">
+        <is>
+          <t>FY25 results announcement, +57.3% YoY</t>
+        </is>
+      </c>
+      <c r="G8" s="74" t="inlineStr">
+        <is>
+          <t>Confirmed by multiple outlets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="73" t="inlineStr">
+        <is>
+          <t>NPAT FY25 (adjusted)</t>
+        </is>
+      </c>
+      <c r="C9" s="73" t="inlineStr">
+        <is>
+          <t>4,694</t>
+        </is>
+      </c>
+      <c r="D9" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E9" s="73" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="F9" s="74" t="inlineStr">
+        <is>
+          <t>Ex one-off financial income (Vincom Center Nguyen Chi Thanh stake transfer), +16.3% YoY</t>
+        </is>
+      </c>
+      <c r="G9" s="74" t="inlineStr">
+        <is>
+          <t>"Adjusted" applies to PROFIT ONLY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="73" t="inlineStr">
+        <is>
+          <t>NPAT FY25 (our model base)</t>
+        </is>
+      </c>
+      <c r="C10" s="73" t="inlineStr">
+        <is>
+          <t>6,367</t>
+        </is>
+      </c>
+      <c r="D10" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E10" s="73" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="F10" s="74" t="inlineStr">
+        <is>
+          <t>VRE_1Q26_v2_linked2.xlsx Summary!K158</t>
+        </is>
+      </c>
+      <c r="G10" s="74" t="inlineStr">
+        <is>
+          <t>Used as the col-H growth denominator for cross-ticker consistency; differs from the 6,446 reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="71" t="inlineStr"/>
+      <c r="B11" s="72" t="inlineStr">
+        <is>
+          <t>VRE — 1Q26 REPORTED</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr"/>
+      <c r="D11" s="71" t="inlineStr"/>
+      <c r="E11" s="71" t="inlineStr"/>
+      <c r="F11" s="71" t="inlineStr"/>
+      <c r="G11" s="71" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>Net revenue 1Q26</t>
+        </is>
+      </c>
+      <c r="C12" s="73" t="inlineStr">
+        <is>
+          <t>2,574</t>
+        </is>
+      </c>
+      <c r="D12" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E12" s="73" t="inlineStr">
+        <is>
+          <t>PRESS</t>
+        </is>
+      </c>
+      <c r="F12" s="74" t="inlineStr">
+        <is>
+          <t>1Q26 results coverage, +20.7% YoY</t>
+        </is>
+      </c>
+      <c r="G12" s="74" t="inlineStr">
+        <is>
+          <t>Reported figure. Earlier draft wrongly labelled this "adjusted" — corrected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="73" t="inlineStr">
+        <is>
+          <t>NPAT 1Q26</t>
+        </is>
+      </c>
+      <c r="C13" s="73" t="inlineStr">
+        <is>
+          <t>1,606</t>
+        </is>
+      </c>
+      <c r="D13" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E13" s="73" t="inlineStr">
+        <is>
+          <t>PRESS</t>
+        </is>
+      </c>
+      <c r="F13" s="74" t="inlineStr">
+        <is>
+          <t>1Q26 results coverage, +36.4% YoY</t>
+        </is>
+      </c>
+      <c r="G13" s="74" t="inlineStr">
+        <is>
+          <t>Confirmed by multiple outlets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="71" t="inlineStr"/>
+      <c r="B14" s="72" t="inlineStr">
+        <is>
+          <t>VRE — FY26F</t>
+        </is>
+      </c>
+      <c r="C14" s="71" t="inlineStr"/>
+      <c r="D14" s="71" t="inlineStr"/>
+      <c r="E14" s="71" t="inlineStr"/>
+      <c r="F14" s="71" t="inlineStr"/>
+      <c r="G14" s="71" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" s="73" t="inlineStr">
+        <is>
+          <t>FY26 revenue plan</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="inlineStr">
+        <is>
+          <t>10,132</t>
+        </is>
+      </c>
+      <c r="D15" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E15" s="73" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="F15" s="74" t="inlineStr">
+        <is>
+          <t>2026 AGM, 23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G15" s="74" t="inlineStr">
+        <is>
+          <t>Board-approved plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>FY26 NPAT plan</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>5,375</t>
+        </is>
+      </c>
+      <c r="D16" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E16" s="73" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="F16" s="74" t="inlineStr">
+        <is>
+          <t>2026 AGM, 23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G16" s="74" t="inlineStr">
+        <is>
+          <t>Board-approved plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="73" t="inlineStr">
+        <is>
+          <t>MAS FY26F net revenue</t>
+        </is>
+      </c>
+      <c r="C17" s="73" t="inlineStr">
+        <is>
+          <t>10,639</t>
+        </is>
+      </c>
+      <c r="D17" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E17" s="73" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F17" s="74">
+        <f> plan x 1.05, per analyst instruction</f>
+        <v/>
+      </c>
+      <c r="G17" s="74" t="inlineStr">
+        <is>
+          <t>Build: 10,132 x 1.05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="73" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="73" t="inlineStr">
+        <is>
+          <t>MAS FY26F NPATMI</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="inlineStr">
+        <is>
+          <t>5,483</t>
+        </is>
+      </c>
+      <c r="D18" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E18" s="73" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F18" s="74">
+        <f> plan x 1.02, per analyst instruction</f>
+        <v/>
+      </c>
+      <c r="G18" s="74" t="inlineStr">
+        <is>
+          <t>Build: 5,375 x 1.02. Implies a 51.5% net margin vs ~53.0% in plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="71" t="inlineStr"/>
+      <c r="B19" s="72" t="inlineStr">
+        <is>
+          <t>VRE — FY27F BUILD (adopted)</t>
+        </is>
+      </c>
+      <c r="C19" s="71" t="inlineStr"/>
+      <c r="D19" s="71" t="inlineStr"/>
+      <c r="E19" s="71" t="inlineStr"/>
+      <c r="F19" s="71" t="inlineStr"/>
+      <c r="G19" s="71" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>FY26F NPATMI base</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="inlineStr">
+        <is>
+          <t>5,483</t>
+        </is>
+      </c>
+      <c r="D20" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E20" s="73" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F20" s="74" t="inlineStr">
+        <is>
+          <t>row 11</t>
+        </is>
+      </c>
+      <c r="G20" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="73" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B21" s="73" t="inlineStr">
+        <is>
+          <t>+ organic leasing growth</t>
+        </is>
+      </c>
+      <c r="C21" s="73" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="D21" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E21" s="73" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F21" s="74" t="inlineStr">
+        <is>
+          <t>+8.0% on base: 2026 GFA additions annualise; occupancy 88.1% (end-2025) recovering</t>
+        </is>
+      </c>
+      <c r="G21" s="74" t="inlineStr">
+        <is>
+          <t>GFA +5.2% in the model; +8% profit growth assumes modest operating leverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B22" s="75" t="inlineStr">
+        <is>
+          <t>+ shophouse handover</t>
+        </is>
+      </c>
+      <c r="C22" s="75" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D22" s="75" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E22" s="75" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F22" s="76" t="inlineStr">
+        <is>
+          <t>~22% of the VND1,575bn guided first-year gross profit, taxed at 20%</t>
+        </is>
+      </c>
+      <c r="G22" s="76" t="inlineStr">
+        <is>
+          <t>DELIBERATELY HAIRCUT — see conflicts below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="77" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="77">
+        <f> FY27F NPATMI</f>
+        <v/>
+      </c>
+      <c r="C23" s="77" t="inlineStr">
+        <is>
+          <t>6,196</t>
+        </is>
+      </c>
+      <c r="D23" s="77" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E23" s="77" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F23" s="78" t="inlineStr">
+        <is>
+          <t>rows 12+13+14</t>
+        </is>
+      </c>
+      <c r="G23" s="78" t="inlineStr">
+        <is>
+          <t>+13.0% YoY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="71" t="inlineStr"/>
+      <c r="B24" s="72" t="inlineStr">
+        <is>
+          <t>FY27F SCENARIOS</t>
+        </is>
+      </c>
+      <c r="C24" s="71" t="inlineStr"/>
+      <c r="D24" s="71" t="inlineStr"/>
+      <c r="E24" s="71" t="inlineStr"/>
+      <c r="F24" s="71" t="inlineStr"/>
+      <c r="G24" s="71" t="inlineStr"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="73" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="73" t="inlineStr">
+        <is>
+          <t>Low — leasing only, no shophouse</t>
+        </is>
+      </c>
+      <c r="C25" s="73" t="inlineStr">
+        <is>
+          <t>5,922</t>
+        </is>
+      </c>
+      <c r="D25" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E25" s="73" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F25" s="74" t="inlineStr">
+        <is>
+          <t>5,483 x 1.08</t>
+        </is>
+      </c>
+      <c r="G25" s="74" t="inlineStr">
+        <is>
+          <t>+8.0% YoY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="77" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="77" t="inlineStr">
+        <is>
+          <t>Base — adopted</t>
+        </is>
+      </c>
+      <c r="C26" s="77" t="inlineStr">
+        <is>
+          <t>6,196</t>
+        </is>
+      </c>
+      <c r="D26" s="77" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E26" s="77" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F26" s="78" t="inlineStr">
+        <is>
+          <t>row 15</t>
+        </is>
+      </c>
+      <c r="G26" s="78" t="inlineStr">
+        <is>
+          <t>+13.0% YoY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="73" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="73" t="inlineStr">
+        <is>
+          <t>High — full handover</t>
+        </is>
+      </c>
+      <c r="C27" s="73" t="inlineStr">
+        <is>
+          <t>6,580</t>
+        </is>
+      </c>
+      <c r="D27" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E27" s="73" t="inlineStr">
+        <is>
+          <t>MAS</t>
+        </is>
+      </c>
+      <c r="F27" s="74" t="inlineStr">
+        <is>
+          <t>5,483 x 1.20</t>
+        </is>
+      </c>
+      <c r="G27" s="74" t="inlineStr">
+        <is>
+          <t>+20.0% YoY. MBS forecasts 6,502 (+19.2%) on a similar full-handover view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="71" t="inlineStr"/>
+      <c r="B28" s="72" t="inlineStr">
+        <is>
+          <t>SHOPHOUSE PIPELINE — underlying facts</t>
+        </is>
+      </c>
+      <c r="C28" s="71" t="inlineStr"/>
+      <c r="D28" s="71" t="inlineStr"/>
+      <c r="E28" s="71" t="inlineStr"/>
+      <c r="F28" s="71" t="inlineStr"/>
+      <c r="G28" s="71" t="inlineStr"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="73" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B29" s="73" t="inlineStr">
+        <is>
+          <t>Deposit paid for shophouse land</t>
+        </is>
+      </c>
+      <c r="C29" s="73" t="inlineStr">
+        <is>
+          <t>5,480</t>
+        </is>
+      </c>
+      <c r="D29" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E29" s="73" t="inlineStr">
+        <is>
+          <t>PRESS</t>
+        </is>
+      </c>
+      <c r="F29" s="74" t="inlineStr">
+        <is>
+          <t>MarketTimes; deposit made end-2024 for ~109,800 sqm net floor</t>
+        </is>
+      </c>
+      <c r="G29" s="74" t="inlineStr">
+        <is>
+          <t>~1,200 units at Vinhomes Royal Island (~1,000) + Golden Avenue (~280).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B30" s="73" t="inlineStr">
+        <is>
+          <t>Guided gross margin</t>
+        </is>
+      </c>
+      <c r="C30" s="73" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D30" s="73" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E30" s="73" t="inlineStr">
+        <is>
+          <t>PRESS</t>
+        </is>
+      </c>
+      <c r="F30" s="74" t="inlineStr">
+        <is>
+          <t>Broker/press coverage of the shophouse programme</t>
+        </is>
+      </c>
+      <c r="G30" s="74" t="inlineStr">
+        <is>
+          <t>Single-source estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="73" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B31" s="73" t="inlineStr">
+        <is>
+          <t>Guided gross profit, first handover yr</t>
+        </is>
+      </c>
+      <c r="C31" s="73" t="inlineStr">
+        <is>
+          <t>1,575</t>
+        </is>
+      </c>
+      <c r="D31" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E31" s="73" t="inlineStr">
+        <is>
+          <t>PRESS</t>
+        </is>
+      </c>
+      <c r="F31" s="74" t="inlineStr">
+        <is>
+          <t>CafeF, 10-Oct-2025</t>
+        </is>
+      </c>
+      <c r="G31" s="79" t="inlineStr">
+        <is>
+          <t>UNVERIFIED against company disclosure — treat as indicative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="73" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B32" s="73" t="inlineStr">
+        <is>
+          <t>Vincom Collection share of FY26 rev</t>
+        </is>
+      </c>
+      <c r="C32" s="73" t="inlineStr">
+        <is>
+          <t>1.5-2</t>
+        </is>
+      </c>
+      <c r="D32" s="73" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E32" s="73" t="inlineStr">
+        <is>
+          <t>COMPANY</t>
+        </is>
+      </c>
+      <c r="F32" s="74" t="inlineStr">
+        <is>
+          <t>2026 AGM, 23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G32" s="74" t="inlineStr">
+        <is>
+          <t>Confirms the FY26 property contribution is small.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="71" t="inlineStr"/>
+      <c r="B33" s="72" t="inlineStr">
+        <is>
+          <t>KNOWN CONFLICTS &amp; OPEN ITEMS</t>
+        </is>
+      </c>
+      <c r="C33" s="71" t="inlineStr"/>
+      <c r="D33" s="71" t="inlineStr"/>
+      <c r="E33" s="71" t="inlineStr"/>
+      <c r="F33" s="71" t="inlineStr"/>
+      <c r="G33" s="71" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="73" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B34" s="73" t="inlineStr">
+        <is>
+          <t>Shophouse timing has already slipped</t>
+        </is>
+      </c>
+      <c r="C34" s="73" t="inlineStr"/>
+      <c r="D34" s="73" t="inlineStr"/>
+      <c r="E34" s="73" t="inlineStr"/>
+      <c r="F34" s="74" t="inlineStr">
+        <is>
+          <t>CafeF (Oct-2025) put the profit step-up in FY26; the Apr-2026 AGM moved it to "from 2027"</t>
+        </is>
+      </c>
+      <c r="G34" s="79" t="inlineStr">
+        <is>
+          <t>Reason for the haircut in row 14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="73" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B35" s="73" t="inlineStr">
+        <is>
+          <t>Historic volatility of the property line</t>
+        </is>
+      </c>
+      <c r="C35" s="73" t="inlineStr">
+        <is>
+          <t>381-3,433</t>
+        </is>
+      </c>
+      <c r="D35" s="73" t="inlineStr">
+        <is>
+          <t>VNDbn</t>
+        </is>
+      </c>
+      <c r="E35" s="73" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="F35" s="74" t="inlineStr">
+        <is>
+          <t>VRE model IS!r78 "Sale of investment properties", FY18-FY24 range</t>
+        </is>
+      </c>
+      <c r="G35" s="79" t="inlineStr">
+        <is>
+          <t>Handover timing is the single largest swing factor in FY27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="73" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B36" s="73" t="inlineStr">
+        <is>
+          <t>BVPS / P-B basis</t>
+        </is>
+      </c>
+      <c r="C36" s="73" t="inlineStr">
+        <is>
+          <t>22,798 / 25,513</t>
+        </is>
+      </c>
+      <c r="D36" s="73" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="E36" s="73" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+      <c r="F36" s="74" t="inlineStr">
+        <is>
+          <t>VRE model BS!L136 / M136</t>
+        </is>
+      </c>
+      <c r="G36" s="79" t="inlineStr">
+        <is>
+          <t>Model balance sheet embeds LOWER earnings than the forecasts overridden into the Stock Pick tab, so P/B is modestly overstated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="73" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B37" s="73" t="inlineStr">
+        <is>
+          <t>FY28F</t>
+        </is>
+      </c>
+      <c r="C37" s="73" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D37" s="73" t="inlineStr"/>
+      <c r="E37" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="74" t="inlineStr">
+        <is>
+          <t>VRE model and Stock Pick tab both stop at FY27F</t>
+        </is>
+      </c>
+      <c r="G37" s="74" t="inlineStr">
+        <is>
+          <t>No FY28 figure exists; none has been estimated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="73" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B38" s="73" t="inlineStr">
+        <is>
+          <t>A property-led FY27 creates a high FY28 base</t>
+        </is>
+      </c>
+      <c r="C38" s="73" t="inlineStr"/>
+      <c r="D38" s="73" t="inlineStr"/>
+      <c r="E38" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="74" t="inlineStr">
+        <is>
+          <t>Analytical note</t>
+        </is>
+      </c>
+      <c r="G38" s="74" t="inlineStr">
+        <is>
+          <t>Same distortion FY25 one-offs created for FY26 optics.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -8,7 +8,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Pick" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price and Forecast" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Assumptions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1" iterate="1"/>
@@ -1163,7 +1162,7 @@
         <is>
           <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income (chiefly the Vincom Center Nguyen Chi Thanh stake transfer); on an adjusted basis NPAT was VND4,694bn (+16.3% YoY). FY25 net revenue was VND8,712bn, with leasing revenue of VND8,400bn (+8.3% YoY). Momentum carried into 1Q26: net revenue VND2,574bn (+20.7% YoY) and NPAT VND1,606bn (+36.4% YoY).
 We forecast FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI of VND5,483bn only ~2% above the VND5,375bn target — i.e. +22.1% on FY25 revenue and +16.8% on adjusted FY25 NPAT (-13.9% against the one-off-inflated reported FY25 NPAT). The narrower profit beat reflects a net margin of 51.5% vs the ~53.0% implied by plan (~150bp dilution), as pre-operating costs and depreciation on newly opened GFA land ahead of full occupancy.
-FY27F NPATMI VND6,196bn (+13.0% YoY) rests on two identifiable drivers rather than trend growth, with the property leg deliberately haircut (see the Sources &amp; Assumptions tab for the build). (i) Mall lease-up: GFA opened late in 2026 — Vincom Plaza at Wonder City (~27,000 sqm, 3Q26) and J-Town My Lam (4Q26) — contributes only partially in FY26 and annualises in FY27, joined by Vincom Mega Mall Long An (Tay Ninh) due in 2027, against occupancy of 88.1% at end-2025 across 90 malls. (ii) Commercial property transfers: management guides this to become a new earnings driver from 2027, as the ~1,200 shophouses at Vinhomes Royal Island and Vinhomes Golden Avenue (VND5,480bn deposited for ~109,800 sqm; ~45% gross margin) are handed over — the segment is guided at only ~1.5-2% of FY26 revenue, so the step-up falls in FY27. We credit only ~22% of the ~VND1,575bn gross profit management guided for a full handover year, because the schedule has already slipped once (press guidance in Oct-2025 put the step-up in FY26; the Apr-2026 AGM moved it to FY27) and the model's own 'sale of investment properties' line has ranged from VND381bn to VND3,433bn historically. This leaves us ~5% below MBS (FY27 NPAT VND6,502bn, +19.2%), which assumes a fuller handover.</t>
+FY27F NPATMI VND6,305bn (+15.0% YoY) rests on two identifiable drivers rather than trend growth, with the property leg deliberately haircut. (i) Mall lease-up: GFA opened late in 2026 — Vincom Plaza at Wonder City (~27,000 sqm, 3Q26) and J-Town My Lam (4Q26) — contributes only partially in FY26 and annualises in FY27, joined by Vincom Mega Mall Long An (Tay Ninh) due in 2027, against occupancy of 88.1% at end-2025 across 90 malls. (ii) Commercial property transfers: management guides this to become a new earnings driver from 2027, as the ~1,200 shophouses at Vinhomes Royal Island and Vinhomes Golden Avenue (VND5,480bn deposited for ~109,800 sqm; ~45% gross margin) are handed over — the segment is guided at only ~1.5-2% of FY26 revenue, so the step-up falls in FY27. We credit only ~30% of the ~VND1,575bn gross profit management guided for a full handover year, because the schedule has already slipped once (press guidance in Oct-2025 put the step-up in FY26; the Apr-2026 AGM moved it to FY27) and the model's own 'sale of investment properties' line has ranged from VND381bn to VND3,433bn historically. This leaves us ~3% below MBS (FY27 NPAT VND6,502bn, +19.2%), which assumes a fuller handover.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -1176,7 +1175,7 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>- Commercial property transfers are a potential new earnings stream from 2027: ~1,200 shophouses at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposited, ~45% gross margin) under the Vincom Collection format. We treat this as optionality, not a base-case engine - our forecast credits only ~22% of the guided first-year gross profit.
+          <t>- Commercial property transfers are a potential new earnings stream from 2027: ~1,200 shophouses at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposited, ~45% gross margin) under the Vincom Collection format. We treat this as optionality, not a base-case engine - our forecast credits only ~30% of the guided first-year gross profit.
 - Mall pipeline: Wonder City (~27,000 sqm) and J-Town My Lam open in 2H26 and annualise in 2027; Vincom Mega Mall Long An follows in 2027, with management flagging 2028 as the breakout year as transport-infrastructure-linked projects complete (GFA target ~3.5mn sqm post-2030 vs ~1.9mn now).
 - Occupancy maximization across 90 operating malls (88.1% at end-2025) supports leasing revenue growth.
 - First cash dividend in 7 years (10% of par, ~VND2.2tn, paid Jul 2026) signals a shareholder-return shift.
@@ -1187,19 +1186,19 @@
         <v>5483</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>6196</v>
+        <v>6305</v>
       </c>
       <c r="H9" s="62" t="n">
         <v>-0.1388706531264823</v>
       </c>
       <c r="I9" s="62" t="n">
-        <v>0.13003830020062</v>
+        <v>0.1499179281415284</v>
       </c>
       <c r="J9" s="63" t="n">
         <v>11.89256159037024</v>
       </c>
       <c r="K9" s="63" t="n">
-        <v>10.52403408650743</v>
+        <v>10.34209598731166</v>
       </c>
       <c r="L9" s="63" t="n">
         <v>1.228188684873102</v>
@@ -1709,7 +1708,7 @@
         <v>5483</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>6196</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="19" ht="15.6" customFormat="1" customHeight="1" s="1">
@@ -2232,1144 +2231,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="68" t="inlineStr">
-        <is>
-          <t>SOURCES &amp; ASSUMPTIONS — provenance record for every figure used in the Stock Pick tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="69" t="inlineStr">
-        <is>
-          <t>RULE: no figure enters a client-facing cell without a source tag below. MODEL = a cell in our own model · COMPANY = company disclosure/plan/AGM · PRESS = media report (outlet + date) · MAS = our estimate, which must show its build · UNVERIFIED = single unconfirmed source, flagged in red.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="70" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="70" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C4" s="70" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D4" s="70" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E4" s="70" t="inlineStr">
-        <is>
-          <t>Source type</t>
-        </is>
-      </c>
-      <c r="F4" s="70" t="inlineStr">
-        <is>
-          <t>Source detail / date</t>
-        </is>
-      </c>
-      <c r="G4" s="70" t="inlineStr">
-        <is>
-          <t>Status &amp; notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="71" t="inlineStr"/>
-      <c r="B5" s="72" t="inlineStr">
-        <is>
-          <t>VRE — FY25 REPORTED</t>
-        </is>
-      </c>
-      <c r="C5" s="71" t="inlineStr"/>
-      <c r="D5" s="71" t="inlineStr"/>
-      <c r="E5" s="71" t="inlineStr"/>
-      <c r="F5" s="71" t="inlineStr"/>
-      <c r="G5" s="71" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="73" t="inlineStr">
-        <is>
-          <t>Net revenue FY25</t>
-        </is>
-      </c>
-      <c r="C6" s="73" t="inlineStr">
-        <is>
-          <t>8,712</t>
-        </is>
-      </c>
-      <c r="D6" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E6" s="73" t="inlineStr">
-        <is>
-          <t>PRESS + COMPANY</t>
-        </is>
-      </c>
-      <c r="F6" s="74" t="inlineStr">
-        <is>
-          <t>Media reports of FY25 results; cross-checks to the FY26 plan (VND10,132bn stated as +16% YoY -&gt; implies 8,734)</t>
-        </is>
-      </c>
-      <c r="G6" s="74" t="inlineStr">
-        <is>
-          <t>RECONCILED. NOT an adjusted figure — the FY25 one-offs sat in financial income, below the revenue line. Model Summary!K157 shows 9,074 but that column is a 2025F forecast, not actual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="73" t="inlineStr">
-        <is>
-          <t>Leasing revenue FY25</t>
-        </is>
-      </c>
-      <c r="C7" s="73" t="inlineStr">
-        <is>
-          <t>8,400</t>
-        </is>
-      </c>
-      <c r="D7" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E7" s="73" t="inlineStr">
-        <is>
-          <t>PRESS</t>
-        </is>
-      </c>
-      <c r="F7" s="74" t="inlineStr">
-        <is>
-          <t>FY25 results coverage, +8.3% YoY</t>
-        </is>
-      </c>
-      <c r="G7" s="74" t="inlineStr">
-        <is>
-          <t>Single source; consistent with model leasing 2025F of 8,311.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="73" t="inlineStr">
-        <is>
-          <t>NPAT FY25 (reported)</t>
-        </is>
-      </c>
-      <c r="C8" s="73" t="inlineStr">
-        <is>
-          <t>6,446</t>
-        </is>
-      </c>
-      <c r="D8" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E8" s="73" t="inlineStr">
-        <is>
-          <t>COMPANY</t>
-        </is>
-      </c>
-      <c r="F8" s="74" t="inlineStr">
-        <is>
-          <t>FY25 results announcement, +57.3% YoY</t>
-        </is>
-      </c>
-      <c r="G8" s="74" t="inlineStr">
-        <is>
-          <t>Confirmed by multiple outlets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B9" s="73" t="inlineStr">
-        <is>
-          <t>NPAT FY25 (adjusted)</t>
-        </is>
-      </c>
-      <c r="C9" s="73" t="inlineStr">
-        <is>
-          <t>4,694</t>
-        </is>
-      </c>
-      <c r="D9" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E9" s="73" t="inlineStr">
-        <is>
-          <t>COMPANY</t>
-        </is>
-      </c>
-      <c r="F9" s="74" t="inlineStr">
-        <is>
-          <t>Ex one-off financial income (Vincom Center Nguyen Chi Thanh stake transfer), +16.3% YoY</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="inlineStr">
-        <is>
-          <t>"Adjusted" applies to PROFIT ONLY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="73" t="inlineStr">
-        <is>
-          <t>NPAT FY25 (our model base)</t>
-        </is>
-      </c>
-      <c r="C10" s="73" t="inlineStr">
-        <is>
-          <t>6,367</t>
-        </is>
-      </c>
-      <c r="D10" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E10" s="73" t="inlineStr">
-        <is>
-          <t>MODEL</t>
-        </is>
-      </c>
-      <c r="F10" s="74" t="inlineStr">
-        <is>
-          <t>VRE_1Q26_v2_linked2.xlsx Summary!K158</t>
-        </is>
-      </c>
-      <c r="G10" s="74" t="inlineStr">
-        <is>
-          <t>Used as the col-H growth denominator for cross-ticker consistency; differs from the 6,446 reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="71" t="inlineStr"/>
-      <c r="B11" s="72" t="inlineStr">
-        <is>
-          <t>VRE — 1Q26 REPORTED</t>
-        </is>
-      </c>
-      <c r="C11" s="71" t="inlineStr"/>
-      <c r="D11" s="71" t="inlineStr"/>
-      <c r="E11" s="71" t="inlineStr"/>
-      <c r="F11" s="71" t="inlineStr"/>
-      <c r="G11" s="71" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B12" s="73" t="inlineStr">
-        <is>
-          <t>Net revenue 1Q26</t>
-        </is>
-      </c>
-      <c r="C12" s="73" t="inlineStr">
-        <is>
-          <t>2,574</t>
-        </is>
-      </c>
-      <c r="D12" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E12" s="73" t="inlineStr">
-        <is>
-          <t>PRESS</t>
-        </is>
-      </c>
-      <c r="F12" s="74" t="inlineStr">
-        <is>
-          <t>1Q26 results coverage, +20.7% YoY</t>
-        </is>
-      </c>
-      <c r="G12" s="74" t="inlineStr">
-        <is>
-          <t>Reported figure. Earlier draft wrongly labelled this "adjusted" — corrected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="73" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="73" t="inlineStr">
-        <is>
-          <t>NPAT 1Q26</t>
-        </is>
-      </c>
-      <c r="C13" s="73" t="inlineStr">
-        <is>
-          <t>1,606</t>
-        </is>
-      </c>
-      <c r="D13" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E13" s="73" t="inlineStr">
-        <is>
-          <t>PRESS</t>
-        </is>
-      </c>
-      <c r="F13" s="74" t="inlineStr">
-        <is>
-          <t>1Q26 results coverage, +36.4% YoY</t>
-        </is>
-      </c>
-      <c r="G13" s="74" t="inlineStr">
-        <is>
-          <t>Confirmed by multiple outlets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="71" t="inlineStr"/>
-      <c r="B14" s="72" t="inlineStr">
-        <is>
-          <t>VRE — FY26F</t>
-        </is>
-      </c>
-      <c r="C14" s="71" t="inlineStr"/>
-      <c r="D14" s="71" t="inlineStr"/>
-      <c r="E14" s="71" t="inlineStr"/>
-      <c r="F14" s="71" t="inlineStr"/>
-      <c r="G14" s="71" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="73" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B15" s="73" t="inlineStr">
-        <is>
-          <t>FY26 revenue plan</t>
-        </is>
-      </c>
-      <c r="C15" s="73" t="inlineStr">
-        <is>
-          <t>10,132</t>
-        </is>
-      </c>
-      <c r="D15" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E15" s="73" t="inlineStr">
-        <is>
-          <t>COMPANY</t>
-        </is>
-      </c>
-      <c r="F15" s="74" t="inlineStr">
-        <is>
-          <t>2026 AGM, 23-Apr-2026</t>
-        </is>
-      </c>
-      <c r="G15" s="74" t="inlineStr">
-        <is>
-          <t>Board-approved plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B16" s="73" t="inlineStr">
-        <is>
-          <t>FY26 NPAT plan</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="inlineStr">
-        <is>
-          <t>5,375</t>
-        </is>
-      </c>
-      <c r="D16" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E16" s="73" t="inlineStr">
-        <is>
-          <t>COMPANY</t>
-        </is>
-      </c>
-      <c r="F16" s="74" t="inlineStr">
-        <is>
-          <t>2026 AGM, 23-Apr-2026</t>
-        </is>
-      </c>
-      <c r="G16" s="74" t="inlineStr">
-        <is>
-          <t>Board-approved plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B17" s="73" t="inlineStr">
-        <is>
-          <t>MAS FY26F net revenue</t>
-        </is>
-      </c>
-      <c r="C17" s="73" t="inlineStr">
-        <is>
-          <t>10,639</t>
-        </is>
-      </c>
-      <c r="D17" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E17" s="73" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F17" s="74">
-        <f> plan x 1.05, per analyst instruction</f>
-        <v/>
-      </c>
-      <c r="G17" s="74" t="inlineStr">
-        <is>
-          <t>Build: 10,132 x 1.05.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="73" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B18" s="73" t="inlineStr">
-        <is>
-          <t>MAS FY26F NPATMI</t>
-        </is>
-      </c>
-      <c r="C18" s="73" t="inlineStr">
-        <is>
-          <t>5,483</t>
-        </is>
-      </c>
-      <c r="D18" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E18" s="73" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F18" s="74">
-        <f> plan x 1.02, per analyst instruction</f>
-        <v/>
-      </c>
-      <c r="G18" s="74" t="inlineStr">
-        <is>
-          <t>Build: 5,375 x 1.02. Implies a 51.5% net margin vs ~53.0% in plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="71" t="inlineStr"/>
-      <c r="B19" s="72" t="inlineStr">
-        <is>
-          <t>VRE — FY27F BUILD (adopted)</t>
-        </is>
-      </c>
-      <c r="C19" s="71" t="inlineStr"/>
-      <c r="D19" s="71" t="inlineStr"/>
-      <c r="E19" s="71" t="inlineStr"/>
-      <c r="F19" s="71" t="inlineStr"/>
-      <c r="G19" s="71" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="73" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B20" s="73" t="inlineStr">
-        <is>
-          <t>FY26F NPATMI base</t>
-        </is>
-      </c>
-      <c r="C20" s="73" t="inlineStr">
-        <is>
-          <t>5,483</t>
-        </is>
-      </c>
-      <c r="D20" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E20" s="73" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F20" s="74" t="inlineStr">
-        <is>
-          <t>row 11</t>
-        </is>
-      </c>
-      <c r="G20" s="74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="73" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B21" s="73" t="inlineStr">
-        <is>
-          <t>+ organic leasing growth</t>
-        </is>
-      </c>
-      <c r="C21" s="73" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="D21" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E21" s="73" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F21" s="74" t="inlineStr">
-        <is>
-          <t>+8.0% on base: 2026 GFA additions annualise; occupancy 88.1% (end-2025) recovering</t>
-        </is>
-      </c>
-      <c r="G21" s="74" t="inlineStr">
-        <is>
-          <t>GFA +5.2% in the model; +8% profit growth assumes modest operating leverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="75" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B22" s="75" t="inlineStr">
-        <is>
-          <t>+ shophouse handover</t>
-        </is>
-      </c>
-      <c r="C22" s="75" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="D22" s="75" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E22" s="75" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F22" s="76" t="inlineStr">
-        <is>
-          <t>~22% of the VND1,575bn guided first-year gross profit, taxed at 20%</t>
-        </is>
-      </c>
-      <c r="G22" s="76" t="inlineStr">
-        <is>
-          <t>DELIBERATELY HAIRCUT — see conflicts below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="77" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B23" s="77">
-        <f> FY27F NPATMI</f>
-        <v/>
-      </c>
-      <c r="C23" s="77" t="inlineStr">
-        <is>
-          <t>6,196</t>
-        </is>
-      </c>
-      <c r="D23" s="77" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E23" s="77" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F23" s="78" t="inlineStr">
-        <is>
-          <t>rows 12+13+14</t>
-        </is>
-      </c>
-      <c r="G23" s="78" t="inlineStr">
-        <is>
-          <t>+13.0% YoY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="71" t="inlineStr"/>
-      <c r="B24" s="72" t="inlineStr">
-        <is>
-          <t>FY27F SCENARIOS</t>
-        </is>
-      </c>
-      <c r="C24" s="71" t="inlineStr"/>
-      <c r="D24" s="71" t="inlineStr"/>
-      <c r="E24" s="71" t="inlineStr"/>
-      <c r="F24" s="71" t="inlineStr"/>
-      <c r="G24" s="71" t="inlineStr"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="73" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B25" s="73" t="inlineStr">
-        <is>
-          <t>Low — leasing only, no shophouse</t>
-        </is>
-      </c>
-      <c r="C25" s="73" t="inlineStr">
-        <is>
-          <t>5,922</t>
-        </is>
-      </c>
-      <c r="D25" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E25" s="73" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F25" s="74" t="inlineStr">
-        <is>
-          <t>5,483 x 1.08</t>
-        </is>
-      </c>
-      <c r="G25" s="74" t="inlineStr">
-        <is>
-          <t>+8.0% YoY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="77" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B26" s="77" t="inlineStr">
-        <is>
-          <t>Base — adopted</t>
-        </is>
-      </c>
-      <c r="C26" s="77" t="inlineStr">
-        <is>
-          <t>6,196</t>
-        </is>
-      </c>
-      <c r="D26" s="77" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E26" s="77" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F26" s="78" t="inlineStr">
-        <is>
-          <t>row 15</t>
-        </is>
-      </c>
-      <c r="G26" s="78" t="inlineStr">
-        <is>
-          <t>+13.0% YoY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="73" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B27" s="73" t="inlineStr">
-        <is>
-          <t>High — full handover</t>
-        </is>
-      </c>
-      <c r="C27" s="73" t="inlineStr">
-        <is>
-          <t>6,580</t>
-        </is>
-      </c>
-      <c r="D27" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E27" s="73" t="inlineStr">
-        <is>
-          <t>MAS</t>
-        </is>
-      </c>
-      <c r="F27" s="74" t="inlineStr">
-        <is>
-          <t>5,483 x 1.20</t>
-        </is>
-      </c>
-      <c r="G27" s="74" t="inlineStr">
-        <is>
-          <t>+20.0% YoY. MBS forecasts 6,502 (+19.2%) on a similar full-handover view.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="71" t="inlineStr"/>
-      <c r="B28" s="72" t="inlineStr">
-        <is>
-          <t>SHOPHOUSE PIPELINE — underlying facts</t>
-        </is>
-      </c>
-      <c r="C28" s="71" t="inlineStr"/>
-      <c r="D28" s="71" t="inlineStr"/>
-      <c r="E28" s="71" t="inlineStr"/>
-      <c r="F28" s="71" t="inlineStr"/>
-      <c r="G28" s="71" t="inlineStr"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="73" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B29" s="73" t="inlineStr">
-        <is>
-          <t>Deposit paid for shophouse land</t>
-        </is>
-      </c>
-      <c r="C29" s="73" t="inlineStr">
-        <is>
-          <t>5,480</t>
-        </is>
-      </c>
-      <c r="D29" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E29" s="73" t="inlineStr">
-        <is>
-          <t>PRESS</t>
-        </is>
-      </c>
-      <c r="F29" s="74" t="inlineStr">
-        <is>
-          <t>MarketTimes; deposit made end-2024 for ~109,800 sqm net floor</t>
-        </is>
-      </c>
-      <c r="G29" s="74" t="inlineStr">
-        <is>
-          <t>~1,200 units at Vinhomes Royal Island (~1,000) + Golden Avenue (~280).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B30" s="73" t="inlineStr">
-        <is>
-          <t>Guided gross margin</t>
-        </is>
-      </c>
-      <c r="C30" s="73" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="D30" s="73" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E30" s="73" t="inlineStr">
-        <is>
-          <t>PRESS</t>
-        </is>
-      </c>
-      <c r="F30" s="74" t="inlineStr">
-        <is>
-          <t>Broker/press coverage of the shophouse programme</t>
-        </is>
-      </c>
-      <c r="G30" s="74" t="inlineStr">
-        <is>
-          <t>Single-source estimate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="73" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B31" s="73" t="inlineStr">
-        <is>
-          <t>Guided gross profit, first handover yr</t>
-        </is>
-      </c>
-      <c r="C31" s="73" t="inlineStr">
-        <is>
-          <t>1,575</t>
-        </is>
-      </c>
-      <c r="D31" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E31" s="73" t="inlineStr">
-        <is>
-          <t>PRESS</t>
-        </is>
-      </c>
-      <c r="F31" s="74" t="inlineStr">
-        <is>
-          <t>CafeF, 10-Oct-2025</t>
-        </is>
-      </c>
-      <c r="G31" s="79" t="inlineStr">
-        <is>
-          <t>UNVERIFIED against company disclosure — treat as indicative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="73" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B32" s="73" t="inlineStr">
-        <is>
-          <t>Vincom Collection share of FY26 rev</t>
-        </is>
-      </c>
-      <c r="C32" s="73" t="inlineStr">
-        <is>
-          <t>1.5-2</t>
-        </is>
-      </c>
-      <c r="D32" s="73" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E32" s="73" t="inlineStr">
-        <is>
-          <t>COMPANY</t>
-        </is>
-      </c>
-      <c r="F32" s="74" t="inlineStr">
-        <is>
-          <t>2026 AGM, 23-Apr-2026</t>
-        </is>
-      </c>
-      <c r="G32" s="74" t="inlineStr">
-        <is>
-          <t>Confirms the FY26 property contribution is small.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="71" t="inlineStr"/>
-      <c r="B33" s="72" t="inlineStr">
-        <is>
-          <t>KNOWN CONFLICTS &amp; OPEN ITEMS</t>
-        </is>
-      </c>
-      <c r="C33" s="71" t="inlineStr"/>
-      <c r="D33" s="71" t="inlineStr"/>
-      <c r="E33" s="71" t="inlineStr"/>
-      <c r="F33" s="71" t="inlineStr"/>
-      <c r="G33" s="71" t="inlineStr"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="73" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B34" s="73" t="inlineStr">
-        <is>
-          <t>Shophouse timing has already slipped</t>
-        </is>
-      </c>
-      <c r="C34" s="73" t="inlineStr"/>
-      <c r="D34" s="73" t="inlineStr"/>
-      <c r="E34" s="73" t="inlineStr"/>
-      <c r="F34" s="74" t="inlineStr">
-        <is>
-          <t>CafeF (Oct-2025) put the profit step-up in FY26; the Apr-2026 AGM moved it to "from 2027"</t>
-        </is>
-      </c>
-      <c r="G34" s="79" t="inlineStr">
-        <is>
-          <t>Reason for the haircut in row 14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="73" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B35" s="73" t="inlineStr">
-        <is>
-          <t>Historic volatility of the property line</t>
-        </is>
-      </c>
-      <c r="C35" s="73" t="inlineStr">
-        <is>
-          <t>381-3,433</t>
-        </is>
-      </c>
-      <c r="D35" s="73" t="inlineStr">
-        <is>
-          <t>VNDbn</t>
-        </is>
-      </c>
-      <c r="E35" s="73" t="inlineStr">
-        <is>
-          <t>MODEL</t>
-        </is>
-      </c>
-      <c r="F35" s="74" t="inlineStr">
-        <is>
-          <t>VRE model IS!r78 "Sale of investment properties", FY18-FY24 range</t>
-        </is>
-      </c>
-      <c r="G35" s="79" t="inlineStr">
-        <is>
-          <t>Handover timing is the single largest swing factor in FY27.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="73" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B36" s="73" t="inlineStr">
-        <is>
-          <t>BVPS / P-B basis</t>
-        </is>
-      </c>
-      <c r="C36" s="73" t="inlineStr">
-        <is>
-          <t>22,798 / 25,513</t>
-        </is>
-      </c>
-      <c r="D36" s="73" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="E36" s="73" t="inlineStr">
-        <is>
-          <t>MODEL</t>
-        </is>
-      </c>
-      <c r="F36" s="74" t="inlineStr">
-        <is>
-          <t>VRE model BS!L136 / M136</t>
-        </is>
-      </c>
-      <c r="G36" s="79" t="inlineStr">
-        <is>
-          <t>Model balance sheet embeds LOWER earnings than the forecasts overridden into the Stock Pick tab, so P/B is modestly overstated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="73" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B37" s="73" t="inlineStr">
-        <is>
-          <t>FY28F</t>
-        </is>
-      </c>
-      <c r="C37" s="73" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D37" s="73" t="inlineStr"/>
-      <c r="E37" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="74" t="inlineStr">
-        <is>
-          <t>VRE model and Stock Pick tab both stop at FY27F</t>
-        </is>
-      </c>
-      <c r="G37" s="74" t="inlineStr">
-        <is>
-          <t>No FY28 figure exists; none has been estimated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="73" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="B38" s="73" t="inlineStr">
-        <is>
-          <t>A property-led FY27 creates a high FY28 base</t>
-        </is>
-      </c>
-      <c r="C38" s="73" t="inlineStr"/>
-      <c r="D38" s="73" t="inlineStr"/>
-      <c r="E38" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="74" t="inlineStr">
-        <is>
-          <t>Analytical note</t>
-        </is>
-      </c>
-      <c r="G38" s="74" t="inlineStr">
-        <is>
-          <t>Same distortion FY25 one-offs created for FY26 optics.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:G2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1201,10 +1201,10 @@
         <v>10.34209598731166</v>
       </c>
       <c r="L9" s="63" t="n">
-        <v>1.228188684873102</v>
+        <v>1.29853340772708</v>
       </c>
       <c r="M9" s="63" t="n">
-        <v>1.097475414590936</v>
+        <v>1.202617731006781</v>
       </c>
     </row>
     <row r="10" ht="153.6" customFormat="1" customHeight="1" s="52">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1160,9 +1160,9 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>FY25 NPAT hit a record VND6,446bn (+57.3% YoY), flattered by one-off financial income (chiefly the Vincom Center Nguyen Chi Thanh stake transfer); on an adjusted basis NPAT was VND4,694bn (+16.3% YoY). FY25 net revenue was VND8,712bn, with leasing revenue of VND8,400bn (+8.3% YoY). Momentum carried into 1Q26: net revenue VND2,574bn (+20.7% YoY) and NPAT VND1,606bn (+36.4% YoY).
-We forecast FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI of VND5,483bn only ~2% above the VND5,375bn target — i.e. +22.1% on FY25 revenue and +16.8% on adjusted FY25 NPAT (-13.9% against the one-off-inflated reported FY25 NPAT). The narrower profit beat reflects a net margin of 51.5% vs the ~53.0% implied by plan (~150bp dilution), as pre-operating costs and depreciation on newly opened GFA land ahead of full occupancy.
-FY27F NPATMI VND6,305bn (+15.0% YoY) rests on two identifiable drivers rather than trend growth, with the property leg deliberately haircut. (i) Mall lease-up: GFA opened late in 2026 — Vincom Plaza at Wonder City (~27,000 sqm, 3Q26) and J-Town My Lam (4Q26) — contributes only partially in FY26 and annualises in FY27, joined by Vincom Mega Mall Long An (Tay Ninh) due in 2027, against occupancy of 88.1% at end-2025 across 90 malls. (ii) Commercial property transfers: management guides this to become a new earnings driver from 2027, as the ~1,200 shophouses at Vinhomes Royal Island and Vinhomes Golden Avenue (VND5,480bn deposited for ~109,800 sqm; ~45% gross margin) are handed over — the segment is guided at only ~1.5-2% of FY26 revenue, so the step-up falls in FY27. We credit only ~30% of the ~VND1,575bn gross profit management guided for a full handover year, because the schedule has already slipped once (press guidance in Oct-2025 put the step-up in FY26; the Apr-2026 AGM moved it to FY27) and the model's own 'sale of investment properties' line has ranged from VND381bn to VND3,433bn historically. This leaves us ~3% below MBS (FY27 NPAT VND6,502bn, +19.2%), which assumes a fuller handover.</t>
+          <t>FY25 NPAT was a record VND6,446bn (+57.3%), flattered by one-off financial income (Vincom Center Nguyen Chi Thanh stake transfer); adjusted NPAT VND4,694bn (+16.3%). FY25 net revenue VND8,712bn, leasing VND8,400bn (+8.3%). 1Q26 carried the momentum: revenue VND2,574bn (+20.7%), NPAT VND1,606bn (+36.4%).
+FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI VND5,483bn only ~2% above the VND5,375bn target — +22.1% on FY25 revenue and +16.8% on adjusted FY25 NPAT (-13.9% vs the one-off-inflated reported base). The narrower profit beat is ~150bp of margin dilution (51.5% vs ~53.0% planned), from pre-operating costs and depreciation on newly opened GFA.
+FY27F NPATMI VND6,305bn (+15.0%) rests on two drivers, with the property leg haircut. (i) Lease-up: Wonder City (~27,000 sqm, 3Q26) and J-Town My Lam (4Q26) annualise, plus Vincom Mega Mall Long An in 2027; occupancy 88.1% across 90 malls. (ii) Property transfers: ~1,200 shophouses at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposited, ~45% GM), guided as a new driver from 2027 (only ~1.5-2% of FY26 revenue). We credit ~30% of the guided VND1,575bn first-year gross profit — the schedule already slipped from FY26 to FY27, and the property line has ranged VND381-3,433bn historically — leaving us ~3% below MBS (VND6,502bn, +19.2%).</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -478,11 +478,6 @@
     <comment ref="F9" authorId="0" shapeId="0">
       <text>
         <t>FY26F: revenue 5% above the 2026 plan (10,132 -&gt; 10,639); NPATMI 2% above plan (5,375 -&gt; 5,483), implying ~150bp net-margin dilution vs plan. FY27F set at +20% YoY (6,580), consistent with VRE's underlying mid-to-high-teens rate; prior 7,194 (+31%) required ~VND13.6tn revenue or a record ~58% margin. Col H growth is vs reported FY25 NPAT (6,367) for cross-ticker consistency; vs adjusted FY25 (4,694) FY26F is +16.8%. Multiples at TP 28,000; shares 2,328.8mn. NOTE: BVPS 26F/27F (22,798/25,513) come from the VRE model's balance sheet, which embeds lower earnings than these overridden forecasts - P/B is therefore modestly overstated.</t>
-      </text>
-    </comment>
-    <comment ref="G9" authorId="0" shapeId="0">
-      <text>
-        <t>FY27F +20% is driver-based, not trend: (i) FY26 mall openings (Wonder City ~27,000 sqm 3Q26; J-Town My Lam 4Q26) annualise, plus Vincom Mega Mall Long An in 2027; (ii) shophouse handovers at Vinhomes Royal Island (~1,000 units) and Golden Avenue (~280 units) - VND5,480bn deposited end-2024 for ~109,800 sqm, ~45% gross margin - which management guides as a new driver from 2027 (only ~1.5-2% of FY26 revenue). Corroborated by MBS: FY27 revenue 13,213 / NPAT 6,502 (+19.2%). Sources: VRE 2026 AGM (23/04/26), CafeF 10/10/25, MarketTimes.</t>
       </text>
     </comment>
     <comment ref="H9" authorId="0" shapeId="0">
@@ -1082,25 +1077,25 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>1H26 (cumulative): revenue VND26,269bn (+12.6% YoY); PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the PBT plan. Technology led: segment revenue VND23,138bn (+15% YoY; 88% of group revenue; Global IT +13.4%, Domestic IT +22.5%), segment PBT VND3,314bn (+16.9% YoY).
-2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (vs VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY).
-We forecast FY26F NPATMI of VND10,943bn (+15.6% YoY), FY27F VND12,518bn (+14.4% YoY) and FY28F VND14,156bn (+13.1% YoY), with FPT Telecom associate income assumed to grow ~15% p.a. FY26F assumptions: Domestic IT +14.0%, Global IT +14.4% (US trimmed to +5.9% on bid-price competition; Japan +22%, EU +18% intact), Education ~+5%.</t>
+          <t>1H26: revenue VND26,269bn (+12.6% YoY) and PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the profit plan. Technology led, with revenue VND23,138bn (+15% YoY, 88% of the group; Global IT +13.4%, Domestic IT +22.5%) and PBT VND3,314bn (+16.9% YoY).
+2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (against VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY).
+We forecast FY26F NPATMI of VND10,943bn (+15.6% YoY), FY27F VND12,518bn (+14.4% YoY) and FY28F VND14,156bn (+13.1% YoY), assuming profit from FPT Telecom grows ~15% a year. FY26F assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition for contracts; Japan +22% and EU +18% unchanged), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
           <t>TP: VND78,750/share
-- DCF (FCFF)-based; revised down from VND91,570.
-- Set at a 25% premium to the current price of ~VND63,000; at TP, FPT trades at 13.0x 2026F P/E vs a 5-year median above 18x.
-- Discount-rate assumptions raised: equity risk premium 7.8% -&gt; 8.9% and terminal growth 2.5% -&gt; 1.5%, reflecting AI-disruption risk to IT-services pricing.</t>
+- Based on discounted cash flow; cut from VND91,570.
+- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.0x 2026F earnings, against a 5-year average above 18x.
+- We now use a higher discount rate and lower long-term growth (equity risk premium 7.8% to 8.9%, terminal growth 2.5% to 1.5%) to reflect the risk that AI lowers prices for IT services.</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>- Government digitalization is the standout driver: Domestic IT grew +22.5% YoY in 6M26 with segment PBT doubling, on public-sector wins under the national digital-transformation programme — a multi-year pipeline insulated from the global IT-spending cycle.
-- AI/digital-transformation demand underpins a Global IT reacceleration (FY27F: +16.7% YoY), led by Japan (+22%) and the EU (+18%).
-- Education capacity (Hue complex) and data-center expansion provide medium-term optionality.
-- Risks: soft US/global IT spending, tariff-related deal delays, JPY/USD FX swings.</t>
+          <t>- Government digitalization is the clearest driver: Domestic IT grew +22.5% YoY in 6M26 and segment profit doubled, on public-sector contract wins under the national digital-transformation programme — work that runs for several years and does not depend on global IT budgets.
+- Demand for AI and digital transformation should lift Global IT growth back to +16.7% in FY27F, led by Japan (+22%) and the EU (+18%).
+- Education capacity (Hue campus) and data-centre expansion could add more over time.
+- Risks: weaker US and global IT spending, contracts delayed by tariffs, and JPY/USD currency swings.</t>
         </is>
       </c>
       <c r="F7" s="61" t="n">
@@ -1160,26 +1155,26 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>FY25 NPAT was a record VND6,446bn (+57.3%), flattered by one-off financial income (Vincom Center Nguyen Chi Thanh stake transfer); adjusted NPAT VND4,694bn (+16.3%). FY25 net revenue VND8,712bn, leasing VND8,400bn (+8.3%). 1Q26 carried the momentum: revenue VND2,574bn (+20.7%), NPAT VND1,606bn (+36.4%).
-FY26F net revenue VND10,639bn (~5% above the VND10,132bn plan) but NPATMI VND5,483bn only ~2% above the VND5,375bn target — +22.1% on FY25 revenue and +16.8% on adjusted FY25 NPAT (-13.9% vs the one-off-inflated reported base). The narrower profit beat is ~150bp of margin dilution (51.5% vs ~53.0% planned), from pre-operating costs and depreciation on newly opened GFA.
-FY27F NPATMI VND6,305bn (+15.0%) rests on two drivers, with the property leg haircut. (i) Lease-up: Wonder City (~27,000 sqm, 3Q26) and J-Town My Lam (4Q26) annualise, plus Vincom Mega Mall Long An in 2027; occupancy 88.1% across 90 malls. (ii) Property transfers: ~1,200 shophouses at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposited, ~45% GM), guided as a new driver from 2027 (only ~1.5-2% of FY26 revenue). We credit ~30% of the guided VND1,575bn first-year gross profit — the schedule already slipped from FY26 to FY27, and the property line has ranged VND381-3,433bn historically — leaving us ~3% below MBS (VND6,502bn, +19.2%).</t>
+          <t>FY25 NPAT was a record VND6,446bn (+57.3%), helped by a one-off gain on the Vincom Center Nguyen Chi Thanh stake sale; excluding it, VND4,694bn (+16.3%). FY25 revenue VND8,712bn, leasing VND8,400bn (+8.3%). 1Q26: revenue VND2,574bn (+20.7%), NPAT VND1,606bn (+36.4%).
+FY26F revenue VND10,639bn, ~5% above the VND10,132bn plan, but NPATMI VND5,483bn only ~2% above the VND5,375bn target. Net margin falls to 51.5% from ~53.0% in plan, as recently opened malls carry costs and depreciation before they are fully let.
+FY27F NPATMI VND6,305bn (+15.0%) from two sources. Malls opened late in 2026 — Wonder City (~27,000 sqm) and J-Town My Lam — run a full year, joined by Vincom Mega Mall Long An; occupancy was 88.1% across 90 malls at end-2025. Shophouses add the rest: ~1,200 units at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposit, ~45% gross margin), which management expects to contribute from 2027. We include only ~30% of the VND1,575bn profit indicated for a full handover year, as timing has slipped once from 2026 and this line has swung between VND381bn and VND3,433bn.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
           <t>TP: VND28,000/share
-- DCF (FCFF)-based; revised down from VND34,000.
-- At TP, VRE trades at 11.9x 2026F P/E and 1.23x 2026F P/B (BVPS26F ~VND22,800) — undemanding for a near-monopoly retail landlord with double-digit leasing growth.
-- Against the current ~VND22,000 (24/07/26), the TP implies ~27% expected return.</t>
+- Based on discounted cash flow; cut from VND34,000.
+- At the target price, VRE trades at 11.9x 2026F earnings and 1.30x 2026F book value (BVPS26F ~VND21,600) — undemanding for the largest mall owner in Vietnam with steady rental growth.
+- Against the current ~VND22,000 (24/07/26), the target implies ~27% upside.</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>- Commercial property transfers are a potential new earnings stream from 2027: ~1,200 shophouses at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposited, ~45% gross margin) under the Vincom Collection format. We treat this as optionality, not a base-case engine - our forecast credits only ~30% of the guided first-year gross profit.
-- Mall pipeline: Wonder City (~27,000 sqm) and J-Town My Lam open in 2H26 and annualise in 2027; Vincom Mega Mall Long An follows in 2027, with management flagging 2028 as the breakout year as transport-infrastructure-linked projects complete (GFA target ~3.5mn sqm post-2030 vs ~1.9mn now).
-- Occupancy maximization across 90 operating malls (88.1% at end-2025) supports leasing revenue growth.
-- First cash dividend in 7 years (10% of par, ~VND2.2tn, paid Jul 2026) signals a shareholder-return shift.
-- Risks: shophouse handover timing is lumpy and largely determines the FY27 step-up; tenant/counterparty concentration in the Vingroup ecosystem; a property-led FY27 creates a high base for FY28, echoing the FY25 one-off distortion.</t>
+          <t>- Shophouse sales could become a new source of earnings from 2027: ~1,200 units at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposit, ~45% gross margin), sold under the Vincom Collection format. We treat this as possible upside rather than a core assumption, including only ~30% of it.
+- New malls: Wonder City (~27,000 sqm) and J-Town My Lam open in 2H26 and run a full year in 2027; Vincom Mega Mall Long An follows in 2027. Management points to 2028 as the bigger year, when projects tied to new transport links complete (floor area target ~3.5mn sqm after 2030, from ~1.9mn now).
+- Filling vacant space across 90 malls (88.1% occupied at end-2025) supports rental growth.
+- First cash dividend in 7 years (10% of par, ~VND2.2tn, paid Jul 2026).
+- Risks: shophouse handover timing is uncertain and largely sets the 2027 result; heavy reliance on Vingroup-related tenants; a property-driven 2027 makes 2028 a harder comparison.</t>
         </is>
       </c>
       <c r="F9" s="61" t="n">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1157,7 +1157,7 @@
         <is>
           <t>FY25 NPAT was a record VND6,446bn (+57.3%), helped by a one-off gain on the Vincom Center Nguyen Chi Thanh stake sale; excluding it, VND4,694bn (+16.3%). FY25 revenue VND8,712bn, leasing VND8,400bn (+8.3%). 1Q26: revenue VND2,574bn (+20.7%), NPAT VND1,606bn (+36.4%).
 FY26F revenue VND10,639bn, ~5% above the VND10,132bn plan, but NPATMI VND5,483bn only ~2% above the VND5,375bn target. Net margin falls to 51.5% from ~53.0% in plan, as recently opened malls carry costs and depreciation before they are fully let.
-FY27F NPATMI VND6,305bn (+15.0%) from two sources. Malls opened late in 2026 — Wonder City (~27,000 sqm) and J-Town My Lam — run a full year, joined by Vincom Mega Mall Long An; occupancy was 88.1% across 90 malls at end-2025. Shophouses add the rest: ~1,200 units at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposit, ~45% gross margin), which management expects to contribute from 2027. We include only ~30% of the VND1,575bn profit indicated for a full handover year, as timing has slipped once from 2026 and this line has swung between VND381bn and VND3,433bn.</t>
+FY27F NPATMI VND6,305bn (+15.0%) comes from two sources. Malls opened late in 2026 — Wonder City (~27,000 sqm) and J-Town My Lam — run a full year, joined by Vincom Mega Mall Long An; occupancy was 88.1% across 90 malls at end-2025. Shophouses add the rest, and the booking case rests on VRE reselling finished stock rather than building it: it paid a VND5,480bn deposit at end-2024 for ~1,200 units at Vinhomes Royal Island and Golden Avenue, where construction completes through 2026. At the April 2026 AGM management set sales to open from 2027, having deliberately held back to capture better pricing as infrastructure lands. Because the units are already built, handover follows sale within months, so a first tranche can be booked in 2027. We include only ~30% of the ~VND1,575bn gross profit indicated for a full year of handovers — roughly a third of the inventory clearing in year one. The timing has already slipped twice; if sales open late in 2027, recognition moves into 2028.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>- Shophouse sales could become a new source of earnings from 2027: ~1,200 units at Vinhomes Royal Island and Golden Avenue (VND5,480bn deposit, ~45% gross margin), sold under the Vincom Collection format. We treat this as possible upside rather than a core assumption, including only ~30% of it.
+          <t>- Shophouse sales open from 2027 (April 2026 AGM), with ~1,200 units at Vinhomes Royal Island and Golden Avenue already paid for via a VND5,480bn deposit at end-2024 and built out through 2026 — finished stock, so handover and revenue follow sale quickly. ~45% gross margin. We include only ~30% of the first full year's profit; slippage past 2027 is the main risk, having already occurred twice.
 - New malls: Wonder City (~27,000 sqm) and J-Town My Lam open in 2H26 and run a full year in 2027; Vincom Mega Mall Long An follows in 2027. Management points to 2028 as the bigger year, when projects tied to new transport links complete (floor area target ~3.5mn sqm after 2030, from ~1.9mn now).
 - Filling vacant space across 90 malls (88.1% occupied at end-2025) supports rental growth.
 - First cash dividend in 7 years (10% of par, ~VND2.2tn, paid Jul 2026).

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1155,9 +1155,9 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>FY25 NPAT was a record VND6,446bn (+57.3%), helped by a one-off gain on the Vincom Center Nguyen Chi Thanh stake sale; excluding it, VND4,694bn (+16.3%). FY25 revenue VND8,712bn, leasing VND8,400bn (+8.3%). 1Q26: revenue VND2,574bn (+20.7%), NPAT VND1,606bn (+36.4%).
-FY26F revenue VND10,639bn, ~5% above the VND10,132bn plan, but NPATMI VND5,483bn only ~2% above the VND5,375bn target. Net margin falls to 51.5% from ~53.0% in plan, as recently opened malls carry costs and depreciation before they are fully let.
-FY27F NPATMI VND6,305bn (+15.0%) comes from two sources. Malls opened late in 2026 — Wonder City (~27,000 sqm) and J-Town My Lam — run a full year, joined by Vincom Mega Mall Long An; occupancy was 88.1% across 90 malls at end-2025. Shophouses add the rest, and the booking case rests on VRE reselling finished stock rather than building it: it paid a VND5,480bn deposit at end-2024 for ~1,200 units at Vinhomes Royal Island and Golden Avenue, where construction completes through 2026. At the April 2026 AGM management set sales to open from 2027, having deliberately held back to capture better pricing as infrastructure lands. Because the units are already built, handover follows sale within months, so a first tranche can be booked in 2027. We include only ~30% of the ~VND1,575bn gross profit indicated for a full year of handovers — roughly a third of the inventory clearing in year one. The timing has already slipped twice; if sales open late in 2027, recognition moves into 2028.</t>
+          <t>FY25 NPAT was a record VND6,446bn (+57.3%) on a one-off gain from the Vincom Center Nguyen Chi Thanh stake sale; excluding it, VND4,694bn (+16.3%). Revenue VND8,712bn. 1Q26: revenue VND2,574bn (+20.7%), NPAT VND1,606bn (+36.4%).
+FY26F revenue VND10,639bn and NPATMI VND5,483bn, ~5% and ~2% above the VND10,132bn/VND5,375bn plan; net margin slips to 51.5% from ~53.0% as new malls carry costs before being fully let.
+FY27F NPATMI VND6,305bn (+15.0%): malls opened in 2026 run a full year, plus Vincom Mega Mall Long An; occupancy 88.1% at end-2025. Shophouses swing the rest — VND5,480bn deposited end-2024 for land at Vinhomes Royal Island and Golden Avenue (~1,200 units), sales from 2027 after two delays. Revenue books on handover, so 2027 needs construction finished by then; we credit ~30% of a full year's profit.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>- Shophouse sales open from 2027 (April 2026 AGM), with ~1,200 units at Vinhomes Royal Island and Golden Avenue already paid for via a VND5,480bn deposit at end-2024 and built out through 2026 — finished stock, so handover and revenue follow sale quickly. ~45% gross margin. We include only ~30% of the first full year's profit; slippage past 2027 is the main risk, having already occurred twice.
+          <t>- Shophouses: VND5,480bn deposited at end-2024 for commercial land at Vinhomes Royal Island and Golden Avenue (~1,200 units, ~45% gross margin). Sales open from 2027 per the April 2026 AGM, twice delayed from 2025. Revenue books on handover, so this is upside rather than a core assumption — we include only ~30% of a full year's profit.
 - New malls: Wonder City (~27,000 sqm) and J-Town My Lam open in 2H26 and run a full year in 2027; Vincom Mega Mall Long An follows in 2027. Management points to 2028 as the bigger year, when projects tied to new transport links complete (floor area target ~3.5mn sqm after 2030, from ~1.9mn now).
 - Filling vacant space across 90 malls (88.1% occupied at end-2025) supports rental growth.
 - First cash dividend in 7 years (10% of par, ~VND2.2tn, paid Jul 2026).

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1079,14 +1079,14 @@
         <is>
           <t>1H26: revenue VND26,269bn (+12.6% YoY) and PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the profit plan. Technology led, with revenue VND23,138bn (+15% YoY, 88% of the group; Global IT +13.4%, Domestic IT +22.5%) and PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (against VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY).
-We forecast FY26F NPATMI of VND10,943bn (+15.6% YoY), FY27F VND12,518bn (+14.4% YoY) and FY28F VND14,156bn (+13.1% YoY), assuming profit from FPT Telecom grows ~15% a year. FY26F assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition for contracts; Japan +22% and EU +18% unchanged), Education ~+5%.</t>
+We forecast FY26F NPATMI of VND10,943bn (+15.6% YoY), FY27F VND12,692bn (+16.0% YoY) and FY28F VND14,787bn (+16.5% YoY), assuming profit from FPT Telecom grows ~15% a year. The FY27-28F upgrade comes from operating leverage rather than pricing: SG&amp;A falls from 17.6% of sales to 17.1% and 16.5%, with revenue and gross margin unchanged. FY26F assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition for contracts; Japan +22% and EU +18% unchanged), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
           <t>TP: VND78,750/share
 - Based on discounted cash flow; cut from VND91,570.
-- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.0x 2026F earnings, against a 5-year average above 18x.
+- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.0x 2026F and 11.2x 2027F earnings, against a 5-year average above 18x.
 - We now use a higher discount rate and lower long-term growth (equity risk premium 7.8% to 8.9%, terminal growth 2.5% to 1.5%) to reflect the risk that AI lowers prices for IT services.</t>
         </is>
       </c>
@@ -1102,25 +1102,25 @@
         <v>10943</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12518</v>
+        <v>12692</v>
       </c>
       <c r="H7" s="62" t="n">
         <v>0.1563010506263802</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.1438998598283892</v>
+        <v>0.1598282006762315</v>
       </c>
       <c r="J7" s="63" t="n">
         <v>13.02516403862665</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>11.38662963083212</v>
+        <v>11.23049952726127</v>
       </c>
       <c r="L7" s="63" t="n">
         <v>3.13626652256712</v>
       </c>
       <c r="M7" s="63" t="n">
-        <v>2.653241138973259</v>
+        <v>2.64529998799705</v>
       </c>
     </row>
     <row r="8" ht="128.4" customFormat="1" customHeight="1" s="39">
@@ -1665,7 +1665,7 @@
         <v>10943</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12518</v>
+        <v>12692</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1077,16 +1077,16 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>1H26: revenue VND26,269bn (+12.6% YoY) and PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the profit plan. Technology led, with revenue VND23,138bn (+15% YoY, 88% of the group; Global IT +13.4%, Domestic IT +22.5%) and PBT VND3,314bn (+16.9% YoY).
-2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (against VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY).
-We forecast FY26F NPATMI of VND10,943bn (+15.6% YoY), FY27F VND12,692bn (+16.0% YoY) and FY28F VND14,787bn (+16.5% YoY), assuming profit from FPT Telecom grows ~15% a year. The FY27-28F upgrade comes from operating leverage rather than pricing: SG&amp;A falls from 17.6% of sales to 17.1% and 16.5%, with revenue and gross margin unchanged. FY26F assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition for contracts; Japan +22% and EU +18% unchanged), Education ~+5%.</t>
+          <t xml:space="preserve">1H26: revenue VND26,269bn (+12.6% YoY) and PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the profit plan. Technology led, with revenue VND23,138bn (+15% YoY, 88% of the group; Global IT +13.4%, Domestic IT +22.5%) and PBT VND3,314bn (+16.9% YoY).
+2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (against VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY). Note that 1H26 NPATMI grew 14.2% against PBT +18.1%: equity income from FPT Telecom is already taxed at the investee, so PBT growth overstates the growth accruing to shareholders. Both quarters show the same wedge (1Q26 +14.4%, 2Q26 +14.0%).
+We forecast FY26F NPATMI of VND10,848bn (+14.6% YoY), FY27F VND12,549bn (+15.7% YoY) and FY28F VND14,608bn (+16.4% YoY), taking 2H26 NPATMI at +15% YoY. FPT Telecom is equity-accounted from FY26: its 1H26 NPATMI of VND1,877bn gives FPT (45.66%) VND857bn, so we carry associate income at VND1,850bn in FY26F growing ~14% a year, in line with FPT Telecom's own 1H26 growth, and tax only the consolidated block at the 12.0% rate implied by the 1H26 print. FY27-28F also assume operating leverage: SG&amp;A falls from 17.6% of sales to 17.1% and 16.5%, with revenue and gross margin unchanged. FY26F assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition for contracts; Japan +22% and EU +18% unchanged), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
-          <t>TP: VND78,750/share
+          <t xml:space="preserve">TP: VND78,750/share
 - Based on discounted cash flow; cut from VND91,570.
-- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.0x 2026F and 11.2x 2027F earnings, against a 5-year average above 18x.
+- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.1x 2026F and 11.4x 2027F earnings, against a 5-year average above 18x.
 - We now use a higher discount rate and lower long-term growth (equity risk premium 7.8% to 8.9%, terminal growth 2.5% to 1.5%) to reflect the risk that AI lowers prices for IT services.</t>
         </is>
       </c>
@@ -1099,22 +1099,22 @@
         </is>
       </c>
       <c r="F7" s="61" t="n">
-        <v>10943</v>
+        <v>10848</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12692</v>
+        <v>12549</v>
       </c>
       <c r="H7" s="62" t="n">
-        <v>0.1563010506263802</v>
+        <v>0.14621899883349387</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.1598282006762315</v>
+        <v>0.15680309734513265</v>
       </c>
       <c r="J7" s="63" t="n">
-        <v>13.02516403862665</v>
+        <v>13.139230279746629</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>11.23049952726127</v>
+        <v>11.358225362554101</v>
       </c>
       <c r="L7" s="63" t="n">
         <v>3.13626652256712</v>
@@ -1662,10 +1662,10 @@
         <v>78750</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>10943</v>
+        <v>10848</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12692</v>
+        <v>12549</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1078,8 +1078,8 @@
       <c r="C7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1H26: revenue VND26,269bn (+12.6% YoY) and PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the profit plan. Technology led, with revenue VND23,138bn (+15% YoY, 88% of the group; Global IT +13.4%, Domestic IT +22.5%) and PBT VND3,314bn (+16.9% YoY).
-2Q26 alone: revenue VND13,789bn; PBT VND2,910bn (against VND12,480bn / VND2,804bn in 1Q26); NPATMI VND2,568bn (+14% YoY). Note that 1H26 NPATMI grew 14.2% against PBT +18.1%: equity income from FPT Telecom is already taxed at the investee, so PBT growth overstates the growth accruing to shareholders. Both quarters show the same wedge (1Q26 +14.4%, 2Q26 +14.0%).
-We forecast FY26F NPATMI of VND10,848bn (+14.6% YoY), FY27F VND12,549bn (+15.7% YoY) and FY28F VND14,608bn (+16.4% YoY), taking 2H26 NPATMI at +15% YoY. FPT Telecom is equity-accounted from FY26: its 1H26 NPATMI of VND1,877bn gives FPT (45.66%) VND857bn, so we carry associate income at VND1,850bn in FY26F growing ~14% a year, in line with FPT Telecom's own 1H26 growth, and tax only the consolidated block at the 12.0% rate implied by the 1H26 print. FY27-28F also assume operating leverage: SG&amp;A falls from 17.6% of sales to 17.1% and 16.5%, with revenue and gross margin unchanged. FY26F assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition for contracts; Japan +22% and EU +18% unchanged), Education ~+5%.</t>
+2Q26 alone: revenue VND13,789bn; PBT VND2,910bn; NPATMI VND2,568bn (+14% YoY). NPATMI grew 14.2% in 1H26 against PBT +18.1% — equity income is already taxed at the investee, so PBT growth overstates what accrues to shareholders (1Q26 +14.4%, 2Q26 +14.0%).
+We forecast FY26F NPATMI of VND10,848bn (+14.6% YoY), FY27F VND12,549bn (+15.7% YoY) and FY28F VND14,608bn (+16.4% YoY), taking 2H26 at +15% YoY. Rebased on the 1H26 consolidated FS filed 21/07/26: gross margin held at 32.4%, operating expenses at 17.6% of sales, tax at 15.6% on the consolidated block only, and minority interest at nil (1H26: -VND8bn). Associate income from FPT Telecom (45.66%), FPT Retail (46.54%), Synnex FPT (48.00%) and FPT Online was VND1,423bn in 1H26; we carry VND2,847bn in FY26F growing ~14% a year. Net financial income of VND830bn holds the 5.86% yield the VND19.4tn term-deposit book earned in 1H26 on a base compounding ~11% a year, assuming no further FX gains or investment provisions. FY26F revenue assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1079,21 +1079,21 @@
         <is>
           <t xml:space="preserve">1H26: revenue VND26,269bn (+12.6% YoY) and PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the profit plan. Technology led, with revenue VND23,138bn (+15% YoY, 88% of the group; Global IT +13.4%, Domestic IT +22.5%) and PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn; NPATMI VND2,568bn (+14% YoY). NPATMI grew 14.2% in 1H26 against PBT +18.1% — equity income is already taxed at the investee, so PBT growth overstates what accrues to shareholders (1Q26 +14.4%, 2Q26 +14.0%).
-We forecast FY26F NPATMI of VND10,848bn (+14.6% YoY), FY27F VND12,549bn (+15.7% YoY) and FY28F VND14,608bn (+16.4% YoY), taking 2H26 at +15% YoY. Rebased on the 1H26 consolidated FS filed 21/07/26: gross margin held at 32.4%, operating expenses at 17.6% of sales, tax at 15.6% on the consolidated block only, and minority interest at nil (1H26: -VND8bn). Associate income from FPT Telecom (45.66%), FPT Retail (46.54%), Synnex FPT (48.00%) and FPT Online was VND1,423bn in 1H26; we carry VND2,847bn in FY26F growing ~14% a year. Net financial income of VND830bn holds the 5.86% yield the VND19.4tn term-deposit book earned in 1H26 on a base compounding ~11% a year, assuming no further FX gains or investment provisions. FY26F revenue assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition), Education ~+5%.</t>
+We forecast FY26F NPATMI of VND10,848bn (+14.6% YoY), FY27F VND12,403bn (+14.3% YoY) and FY28F VND14,100bn (+13.7% YoY), taking 2H26 at +15% YoY. No line accelerates: every growth rate is held at its FY26F level (Global IT +14.7%, Domestic IT +12%, Education +5%) and there is no operating leverage. Rebased on the 1H26 consolidated FS filed 21/07/26: gross margin held at 32.4%, operating expenses flat at 17.6% of sales, tax at 15.6% on the consolidated block only, and minority interest at nil (1H26: -VND8bn). Associate income from FPT Telecom (45.66%), FPT Retail (46.54%), Synnex FPT (48.00%) and FPT Online was VND1,423bn in 1H26; we carry VND2,847bn in FY26F growing ~14% a year. Net financial income of VND830bn holds the 5.86% yield the VND19.4tn term-deposit book earned in 1H26 on a base compounding ~11% a year, assuming no further FX gains or investment provisions. FY26F revenue assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">TP: VND78,750/share
 - Based on discounted cash flow; cut from VND91,570.
-- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.1x 2026F and 11.4x 2027F earnings, against a 5-year average above 18x.
+- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.1x 2026F and 11.5x 2027F earnings, against a 5-year average above 18x.
 - We now use a higher discount rate and lower long-term growth (equity risk premium 7.8% to 8.9%, terminal growth 2.5% to 1.5%) to reflect the risk that AI lowers prices for IT services.</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>- Government digitalization is the clearest driver: Domestic IT grew +22.5% YoY in 6M26 and segment profit doubled, on public-sector contract wins under the national digital-transformation programme — work that runs for several years and does not depend on global IT budgets.
-- Demand for AI and digital transformation should lift Global IT growth back to +16.7% in FY27F, led by Japan (+22%) and the EU (+18%).
+          <t xml:space="preserve">- Government digitalization is the clearest driver: Domestic IT grew +22.5% YoY in 6M26 and segment profit doubled, on public-sector contract wins under the national digital-transformation programme — work that runs for several years and does not depend on global IT budgets.
+- We hold Global IT at +14.7% in FY27-28F, the FY26F rate, against +13.4% delivered in 1H26 — the AI and digital-transformation pipeline supports the pace but we do not assume it accelerates.
 - Education capacity (Hue campus) and data-centre expansion could add more over time.
 - Risks: weaker US and global IT spending, contracts delayed by tariffs, and JPY/USD currency swings.</t>
         </is>
@@ -1102,19 +1102,19 @@
         <v>10848</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12549</v>
+        <v>12403</v>
       </c>
       <c r="H7" s="62" t="n">
         <v>0.14621899883349387</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.15680309734513265</v>
+        <v>0.14334439528023601</v>
       </c>
       <c r="J7" s="63" t="n">
         <v>13.139230279746629</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>11.358225362554101</v>
+        <v>11.492179311456905</v>
       </c>
       <c r="L7" s="63" t="n">
         <v>3.13626652256712</v>
@@ -1665,7 +1665,7 @@
         <v>10848</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12549</v>
+        <v>12403</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1079,21 +1079,21 @@
         <is>
           <t xml:space="preserve">1H26: revenue VND26,269bn (+12.6% YoY) and PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the profit plan. Technology led, with revenue VND23,138bn (+15% YoY, 88% of the group; Global IT +13.4%, Domestic IT +22.5%) and PBT VND3,314bn (+16.9% YoY).
 2Q26 alone: revenue VND13,789bn; PBT VND2,910bn; NPATMI VND2,568bn (+14% YoY). NPATMI grew 14.2% in 1H26 against PBT +18.1% — equity income is already taxed at the investee, so PBT growth overstates what accrues to shareholders (1Q26 +14.4%, 2Q26 +14.0%).
-We forecast FY26F NPATMI of VND10,848bn (+14.6% YoY), FY27F VND12,403bn (+14.3% YoY) and FY28F VND14,100bn (+13.7% YoY), taking 2H26 at +15% YoY. No line accelerates: every growth rate is held at its FY26F level (Global IT +14.7%, Domestic IT +12%, Education +5%) and there is no operating leverage. Rebased on the 1H26 consolidated FS filed 21/07/26: gross margin held at 32.4%, operating expenses flat at 17.6% of sales, tax at 15.6% on the consolidated block only, and minority interest at nil (1H26: -VND8bn). Associate income from FPT Telecom (45.66%), FPT Retail (46.54%), Synnex FPT (48.00%) and FPT Online was VND1,423bn in 1H26; we carry VND2,847bn in FY26F growing ~14% a year. Net financial income of VND830bn holds the 5.86% yield the VND19.4tn term-deposit book earned in 1H26 on a base compounding ~11% a year, assuming no further FX gains or investment provisions. FY26F revenue assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition), Education ~+5%.</t>
+We forecast FY26F NPATMI of VND10,848bn (+14.6% YoY), FY27F VND12,497bn (+15.2% YoY) and FY28F VND14,459bn (+15.7% YoY), taking 2H26 at +15% YoY. The step up in FY27-28F rests on two named assumptions - Global IT reaccelerating to +15.5% then +16.0%, and associate income to +16% from +14% - not on margin: SG&amp;A stays within 16bp of the 17.6% of sales delivered in 1H26. Domestic IT is held at +12% and Education at +5%. Rebased on the 1H26 consolidated FS filed 21/07/26: gross margin held at 32.4%, operating expenses within 16bp of 17.6% of sales, tax at 15.6% on the consolidated block only, and minority interest at nil (1H26: -VND8bn). Associate income from FPT Telecom (45.66%), FPT Retail (46.54%), Synnex FPT (48.00%) and FPT Online was VND1,423bn in 1H26; we carry VND2,847bn in FY26F growing ~14% a year. Net financial income of VND830bn holds the 5.86% yield the VND19.4tn term-deposit book earned in 1H26 on a base compounding ~11% a year, assuming no further FX gains or investment provisions. FY26F revenue assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">TP: VND78,750/share
 - Based on discounted cash flow; cut from VND91,570.
-- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.1x 2026F and 11.5x 2027F earnings, against a 5-year average above 18x.
+- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.1x 2026F and 11.4x 2027F earnings, against a 5-year average above 18x.
 - We now use a higher discount rate and lower long-term growth (equity risk premium 7.8% to 8.9%, terminal growth 2.5% to 1.5%) to reflect the risk that AI lowers prices for IT services.</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">- Government digitalization is the clearest driver: Domestic IT grew +22.5% YoY in 6M26 and segment profit doubled, on public-sector contract wins under the national digital-transformation programme — work that runs for several years and does not depend on global IT budgets.
-- We hold Global IT at +14.7% in FY27-28F, the FY26F rate, against +13.4% delivered in 1H26 — the AI and digital-transformation pipeline supports the pace but we do not assume it accelerates.
+- We look for Global IT to reaccelerate to +15.5% in FY27F and +16.0% in FY28F, from the +14.7% assumed for FY26F and +13.4% delivered in 1H26, as the AI and digital-transformation pipeline converts.
 - Education capacity (Hue campus) and data-centre expansion could add more over time.
 - Risks: weaker US and global IT spending, contracts delayed by tariffs, and JPY/USD currency swings.</t>
         </is>
@@ -1102,19 +1102,19 @@
         <v>10848</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12403</v>
+        <v>12497</v>
       </c>
       <c r="H7" s="62" t="n">
         <v>0.14621899883349387</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.14334439528023601</v>
+        <v>0.15200958702064904</v>
       </c>
       <c r="J7" s="63" t="n">
         <v>13.139230279746629</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>11.492179311456905</v>
+        <v>11.405737376970473</v>
       </c>
       <c r="L7" s="63" t="n">
         <v>3.13626652256712</v>
@@ -1665,7 +1665,7 @@
         <v>10848</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12403</v>
+        <v>12497</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1093,7 +1093,7 @@
       <c r="E7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">- Government digitalization is the clearest driver: Domestic IT grew +22.5% YoY in 6M26 and segment profit doubled, on public-sector contract wins under the national digital-transformation programme — work that runs for several years and does not depend on global IT budgets.
-- We look for Global IT to reaccelerate to +15.5% in FY27F and +16.0% in FY28F, from the +14.7% assumed for FY26F and +13.4% delivered in 1H26, as the AI and digital-transformation pipeline converts.
+- Signed contract value for Global IT reached VND26,338bn in 1H26, +32.3% YoY, with 14 deals above USD10mn (+27.3%) - a book-to-bill of 1.39x against 1.07-1.22x through FY21-25, and the largest half-year backlog build on record. Signings have accelerated (+13.0% FY24, +21.0% FY25, +32.3% 1H26) while recognised revenue decelerated (+27.4%, +14.3%, +13.4%). On that basis we look for Global IT to reaccelerate to +15.5% in FY27F and +16.0% in FY28F.
 - Education capacity (Hue campus) and data-centre expansion could add more over time.
 - Risks: weaker US and global IT spending, contracts delayed by tariffs, and JPY/USD currency swings.</t>
         </is>

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1078,49 +1078,50 @@
       <c r="C7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1H26: revenue VND26,269bn (+12.6% YoY) and PBT VND5,714bn (+18.1% YoY) — 45% of the FY26 revenue plan and 49% of the profit plan. Technology led, with revenue VND23,138bn (+15% YoY, 88% of the group; Global IT +13.4%, Domestic IT +22.5%) and PBT VND3,314bn (+16.9% YoY).
-2Q26 alone: revenue VND13,789bn; PBT VND2,910bn; NPATMI VND2,568bn (+14% YoY). NPATMI grew 14.2% in 1H26 against PBT +18.1% — equity income is already taxed at the investee, so PBT growth overstates what accrues to shareholders (1Q26 +14.4%, 2Q26 +14.0%).
-We forecast FY26F NPATMI of VND10,848bn (+14.6% YoY), FY27F VND12,497bn (+15.2% YoY) and FY28F VND14,459bn (+15.7% YoY), taking 2H26 at +15% YoY. The step up in FY27-28F rests on two named assumptions - Global IT reaccelerating to +15.5% then +16.0%, and associate income to +16% from +14% - not on margin: SG&amp;A stays within 16bp of the 17.6% of sales delivered in 1H26. Domestic IT is held at +12% and Education at +5%. Rebased on the 1H26 consolidated FS filed 21/07/26: gross margin held at 32.4%, operating expenses within 16bp of 17.6% of sales, tax at 15.6% on the consolidated block only, and minority interest at nil (1H26: -VND8bn). Associate income from FPT Telecom (45.66%), FPT Retail (46.54%), Synnex FPT (48.00%) and FPT Online was VND1,423bn in 1H26; we carry VND2,847bn in FY26F growing ~14% a year. Net financial income of VND830bn holds the 5.86% yield the VND19.4tn term-deposit book earned in 1H26 on a base compounding ~11% a year, assuming no further FX gains or investment provisions. FY26F revenue assumptions: Domestic IT +14.0%, Global IT +14.4% (US cut to +5.9% on price competition), Education ~+5%.</t>
+2Q26: revenue VND13,789bn; PBT VND2,910bn; NPATMI VND2,568bn (+14% YoY). Against the restated comparatives FPT published on 21/07/26, 1H26 revenue rose 12.6%, PBT 18.1% and associate income 40.8%.
+We forecast FY26F NPATMI of VND10,944bn (+15.6% YoY), FY27F VND12,674bn (+15.8% YoY) and FY28F VND14,774bn (+16.6% YoY). FPT Telecom is equity-accounted from FY26; associate income including FPT Retail, Synnex FPT and FPT Online reaches VND2,608bn in FY26F. SG&amp;A falls from 17.6% of sales to 17.1% and 16.5% with gross margin unchanged. Revenue assumptions: Domestic IT +14.0%, Global IT +14.7% in FY26F then +16.7%/+17.7% in FY27-28F (US cut to +5.9% on price competition; Japan +22%, EU +18%), Education ~+5%.</t>
         </is>
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TP: VND78,750/share
-- Based on discounted cash flow; cut from VND91,570.
-- Set 25% above the current price of ~VND63,000; at the target price FPT trades at 13.1x 2026F and 11.4x 2027F earnings, against a 5-year average above 18x.
-- We now use a higher discount rate and lower long-term growth (equity risk premium 7.8% to 8.9%, terminal growth 2.5% to 1.5%) to reflect the risk that AI lowers prices for IT services.</t>
+          <t xml:space="preserve">TP: VND87,950/share
+- Based on discounted cash flow; raised from VND78,750.
+- We cut the assumed cost of debt to 9.0% from 11.5%; FPT's realised funding cost in 1H26 was 4.0% (interest expense VND392bn on average debt of VND19,761bn). WACC falls to 11.4%.
+- The equity risk premium stays at 8.97% and terminal growth at 1.5% to carry the risk that AI lowers prices for IT services.
+- Set 23% above the current price of VND71,700; at the target price FPT trades at 13.7x 2026F and 11.8x 2027F earnings, against a 5-year average above 18x.</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">- Government digitalization is the clearest driver: Domestic IT grew +22.5% YoY in 6M26 and segment profit doubled, on public-sector contract wins under the national digital-transformation programme — work that runs for several years and does not depend on global IT budgets.
-- Signed contract value for Global IT reached VND26,338bn in 1H26, +32.3% YoY, with 14 deals above USD10mn (+27.3%) - a book-to-bill of 1.39x against 1.07-1.22x through FY21-25, and the largest half-year backlog build on record. Signings have accelerated (+13.0% FY24, +21.0% FY25, +32.3% 1H26) while recognised revenue decelerated (+27.4%, +14.3%, +13.4%). On that basis we look for Global IT to reaccelerate to +15.5% in FY27F and +16.0% in FY28F.
+- Signed contract value for Global IT reached VND26,338bn in 1H26, +32.3% YoY, with 14 deals above USD10mn (+27.3%) - a book-to-bill of 1.39x against 1.07-1.22x through FY21-25, and the largest half-year backlog build on record. Signings have accelerated (+13.0% FY24, +21.0% FY25, +32.3% 1H26) while recognised revenue decelerated (+27.4%, +14.3%, +13.4%). On that basis we look for Global IT to reaccelerate to +16.7% in FY27F and +17.7% in FY28F.
 - Education capacity (Hue campus) and data-centre expansion could add more over time.
 - Risks: weaker US and global IT spending, contracts delayed by tariffs, and JPY/USD currency swings.</t>
         </is>
       </c>
       <c r="F7" s="61" t="n">
-        <v>10848</v>
+        <v>10944</v>
       </c>
       <c r="G7" s="61" t="n">
-        <v>12497</v>
+        <v>12674</v>
       </c>
       <c r="H7" s="62" t="n">
-        <v>0.14621899883349387</v>
+        <v>0.15631551030413693</v>
       </c>
       <c r="I7" s="62" t="n">
-        <v>0.15200958702064904</v>
+        <v>0.15814504518869787</v>
       </c>
       <c r="J7" s="63" t="n">
-        <v>13.139230279746629</v>
+        <v>13.690565021325336</v>
       </c>
       <c r="K7" s="63" t="n">
-        <v>11.405737376970473</v>
+        <v>11.821114357135395</v>
       </c>
       <c r="L7" s="63" t="n">
-        <v>3.13626652256712</v>
+        <v>3.5017518713170888</v>
       </c>
       <c r="M7" s="63" t="n">
-        <v>2.64529998799705</v>
+        <v>2.9543164259321464</v>
       </c>
     </row>
     <row r="8" ht="128.4" customFormat="1" customHeight="1" s="39">
@@ -1659,13 +1660,13 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>78750</v>
+        <v>87950</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>10848</v>
+        <v>10944</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>12497</v>
+        <v>12674</v>
       </c>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1024,9 +1024,9 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>- We forecast NII at VND27,010bn (+1.2% YoY), supported by 11.7% credit growth, with corporate lending remaining the key growth engine. 
-- NIM is expected to trough at 2.94% (-38bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering to 3.15% (+21bps YoY) in FY27F. 
-- Our FY26F NPL assumption of 4.5% (-1.9%p YoY) requires aggressive write-offs and collateral recovery.</t>
+          <t xml:space="preserve">- We forecast NII at VND27,010bn (+1.2% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
+- NIM is expected to trough at 2.94% (-38bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
+- We move our FY26F NPL assumption to 5.9% from below 4.5%, and FY27F to 4.0% from 3.1%. The revision does not change FY26F provisioning: existing reserves of ~VND21.6tn plus the unchanged VND10.9tn charge fund ~VND8.9tn of 2H26 write-offs (28% of Group 5), enough to take 7.54% to 5.9% at 45% coverage. The former 4.5% required ~VND18tn of write-offs the reserve stock cannot support.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1042,28 +1042,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6583</v>
+        <v>6177</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>12311</v>
+        <v>9890</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.1084357635965651</v>
+        <v>0.04007408654655675</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.8701200060762571</v>
+        <v>0.6011008580216934</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>24.3</v>
+        <v>25.950633755837224</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>13</v>
+        <v>16.204957300562384</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.421789883268482</v>
+        <v>2.4251870324189526</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.037075827398408</v>
+        <v>2.1095444685466376</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1606,10 +1606,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6583</v>
+        <v>6177</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>12311</v>
+        <v>9890</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1026,7 +1026,8 @@
         <is>
           <t xml:space="preserve">- We forecast NII at VND27,010bn (+1.2% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
 - NIM is expected to trough at 2.94% (-38bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We move our FY26F NPL assumption to 5.9% from below 4.5%, and FY27F to 4.0% from 3.1%. The revision does not change FY26F provisioning: existing reserves of ~VND21.6tn plus the unchanged VND10.9tn charge fund ~VND8.9tn of 2H26 write-offs (28% of Group 5), enough to take 7.54% to 5.9% at 45% coverage. The former 4.5% required ~VND18tn of write-offs the reserve stock cannot support.</t>
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage back at 50.0%. Holding coverage at 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- We raise FY26F PBT to VND8,716bn (+14.3% YoY) on the cost line alone: 1H26 CIR came in at 35.6% against the 42.9% previously carried for the full year, and we now assume 39.9% (-0.8%p YoY).</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1042,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6177</v>
+        <v>6786</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>9890</v>
+        <v>10693</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.04007408654655675</v>
+        <v>0.142645759609477</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.6011008580216934</v>
+        <v>0.5757334630063509</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>25.950633755837224</v>
+        <v>23.618214991969115</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>16.204957300562384</v>
+        <v>14.988711953167375</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.4251870324189526</v>
+        <v>2.4027687316828192</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.1095444685466376</v>
+        <v>2.070807486831378</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1606,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6177</v>
+        <v>6786</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>9890</v>
+        <v>10693</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1027,7 +1027,7 @@
           <t xml:space="preserve">- We forecast NII at VND27,010bn (+1.2% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
 - NIM is expected to trough at 2.94% (-38bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
 - We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage back at 50.0%. Holding coverage at 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We raise FY26F PBT to VND8,716bn (+14.3% YoY) on the cost line alone: 1H26 CIR came in at 35.6% against the 42.9% previously carried for the full year, and we now assume 39.9% (-0.8%p YoY).</t>
+- We raise FY26F PBT to VND8,683bn (+13.8% YoY) on the cost line alone: 1H26 CIR came in at 35.6% against the 42.9% previously carried for the full year, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F as total operating income outgrows a cost base held near flat through the clean-up.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6786</v>
+        <v>6761</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>10693</v>
+        <v>11238</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.142645759609477</v>
+        <v>0.1383106337086446</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.5757334630063509</v>
+        <v>0.6622708853592754</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>23.618214991969115</v>
+        <v>23.708162263400226</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>14.988711953167375</v>
+        <v>14.262514294278851</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.4027687316828192</v>
+        <v>2.4036980395777965</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.070807486831378</v>
+        <v>2.0570227332916238</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6786</v>
+        <v>6761</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>10693</v>
+        <v>11238</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1024,10 +1024,10 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">- We forecast NII at VND27,010bn (+1.2% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
-- NIM is expected to trough at 2.94% (-38bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
+          <t xml:space="preserve">- We forecast NII at VND26,712bn (+0.1% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
+- NIM is expected to trough at 2.92% (-40bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
 - We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage back at 50.0%. Holding coverage at 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We raise FY26F PBT to VND8,683bn (+13.8% YoY) on the cost line alone: 1H26 CIR came in at 35.6% against the 42.9% previously carried for the full year, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F as total operating income outgrows a cost base held near flat through the clean-up.</t>
+- We raise FY26F PBT to VND8,507bn (+11.5% YoY) on the cost line alone: 1H26 CIR came in at 35.6% against the 42.9% previously carried for the full year, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F as total operating income outgrows a cost base held near flat through the clean-up.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6761</v>
+        <v>6623</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>11238</v>
+        <v>11427</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.1383106337086446</v>
+        <v>0.11523138039007463</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.6622708853592754</v>
+        <v>0.7251638434077992</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>23.708162263400226</v>
+        <v>24.19879290042856</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>14.262514294278851</v>
+        <v>14.02695343569659</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.4036980395777965</v>
+        <v>2.408649308922513</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.0570227332916238</v>
+        <v>2.0556600341438744</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6761</v>
+        <v>6623</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>11238</v>
+        <v>11427</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1026,8 +1026,8 @@
         <is>
           <t xml:space="preserve">- We forecast NII at VND26,712bn (+0.1% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
 - NIM is expected to trough at 2.92% (-40bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage back at 50.0%. Holding coverage at 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We raise FY26F PBT to VND8,507bn (+11.5% YoY) on the cost line alone: 1H26 CIR came in at 35.6% against the 42.9% previously carried for the full year, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F as total operating income outgrows a cost base held near flat through the clean-up.</t>
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 51.1%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- We set FY26F PBT at VND8,100bn (+6.2% YoY), in line with the board-approved plan. The cost line does the lifting: 1H26 CIR came in at 35.6% against the 42.9% previously carried, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F, with the balance taken back in a provisioning charge of VND11.5tn that holds coverage at 51.1%.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6623</v>
+        <v>6307</v>
       </c>
       <c r="G6" s="61" t="n">
         <v>11427</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.11523138039007463</v>
+        <v>0.061875498625135306</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.7251638434077992</v>
+        <v>0.8118478644377536</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>24.19879290042856</v>
+        <v>25.41470562703468</v>
       </c>
       <c r="K6" s="63" t="n">
         <v>14.02695343569659</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.408649308922513</v>
+        <v>2.4201743863238225</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.0556600341438744</v>
+        <v>2.064048737906604</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,7 +1607,7 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6623</v>
+        <v>6307</v>
       </c>
       <c r="E13" s="15" t="n">
         <v>11427</v>

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1026,8 +1026,8 @@
         <is>
           <t xml:space="preserve">- We forecast NII at VND26,712bn (+0.1% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
 - NIM is expected to trough at 2.92% (-40bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 51.1%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We set FY26F PBT at VND8,100bn (+6.2% YoY), in line with the board-approved plan. The cost line does the lifting: 1H26 CIR came in at 35.6% against the 42.9% previously carried, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F, with the balance taken back in a provisioning charge of VND11.5tn that holds coverage at 51.1%.</t>
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage back at 50.0%. Holding coverage at 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- We set FY26F PBT at VND8,507bn (+11.5% YoY), 5% above the board-approved plan of VND8,100bn. The cost line does the lifting: 1H26 CIR came in at 35.6% against the 42.9% previously carried, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F, on a provisioning charge of VND11.1tn that holds coverage at 50.0%.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6307</v>
+        <v>6623</v>
       </c>
       <c r="G6" s="61" t="n">
         <v>11427</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.061875498625135306</v>
+        <v>0.11523138039007463</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.8118478644377536</v>
+        <v>0.7251638434077992</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>25.41470562703468</v>
+        <v>24.19879290042856</v>
       </c>
       <c r="K6" s="63" t="n">
         <v>14.02695343569659</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.4201743863238225</v>
+        <v>2.408649308922513</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.064048737906604</v>
+        <v>2.0556600341438744</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,7 +1607,7 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6307</v>
+        <v>6623</v>
       </c>
       <c r="E13" s="15" t="n">
         <v>11427</v>

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1026,8 +1026,8 @@
         <is>
           <t xml:space="preserve">- We forecast NII at VND26,712bn (+0.1% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
 - NIM is expected to trough at 2.92% (-40bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage back at 50.0%. Holding coverage at 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We set FY26F PBT at VND8,507bn (+11.5% YoY), 5% above the board-approved plan of VND8,100bn. The cost line does the lifting: 1H26 CIR came in at 35.6% against the 42.9% previously carried, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F, on a provisioning charge of VND11.1tn that holds coverage at 50.0%.</t>
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 51.0%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- We set FY26F PBT at VND8,150bn (+6.9% YoY), marginally above the board-approved plan of VND8,100bn. The cost line does the lifting: 1H26 CIR came in at 35.6% against the 42.9% previously carried, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F, with the balance taken back in a provisioning charge of VND11.4tn that holds coverage at 51.0%.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6623</v>
+        <v>6346</v>
       </c>
       <c r="G6" s="61" t="n">
         <v>11427</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.11523138039007463</v>
+        <v>0.06853515168080859</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.7251638434077992</v>
+        <v>0.8005555095275407</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>24.19879290042856</v>
+        <v>25.256308290529766</v>
       </c>
       <c r="K6" s="63" t="n">
         <v>14.02695343569659</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.408649308922513</v>
+        <v>2.4187298550580487</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.0556600341438744</v>
+        <v>2.062997958224185</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,7 +1607,7 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6623</v>
+        <v>6346</v>
       </c>
       <c r="E13" s="15" t="n">
         <v>11427</v>

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1024,10 +1024,10 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">- We forecast NII at VND26,712bn (+0.1% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
+          <t xml:space="preserve">- We forecast NII at VND26,704bn (+0.1% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
 - NIM is expected to trough at 2.92% (-40bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 51.0%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We set FY26F PBT at VND8,150bn (+6.9% YoY), marginally above the board-approved plan of VND8,100bn. The cost line does the lifting: 1H26 CIR came in at 35.6% against the 42.9% previously carried, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 36.0% in FY28F, with the balance taken back in a provisioning charge of VND11.4tn that holds coverage at 51.0%.</t>
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- We set FY26F PBT at VND8,143bn (+6.7% YoY), marginally above the board-approved plan of VND8,100bn. The cost line does the lifting: 1H26 CIR came in at 35.6% against the 42.9% previously carried, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 35.4% in FY28F, with the balance taken back in a provisioning charge of VND11.4tn that holds coverage at 50.9%.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6346</v>
+        <v>6340</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>11427</v>
+        <v>9572</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.06853515168080859</v>
+        <v>0.06748299535065105</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.8005555095275407</v>
+        <v>0.5097241281408225</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>25.256308290529766</v>
+        <v>26.451026230697643</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>14.02695343569659</v>
+        <v>17.520436838531054</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.4187298550580487</v>
+        <v>2.5308913552671295</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.062997958224185</v>
+        <v>2.2114406440595267</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6346</v>
+        <v>6340</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>11427</v>
+        <v>9572</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1024,10 +1024,10 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">- We forecast NII at VND26,704bn (+0.1% YoY). 1H26 loan growth of 1.5% sits well below the 11.7% carried for the full year, which we flag as the next assumption to re-cut.
-- NIM is expected to trough at 2.92% (-40bps YoY) in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We set FY26F PBT at VND8,143bn (+6.7% YoY), marginally above the board-approved plan of VND8,100bn. The cost line does the lifting: 1H26 CIR came in at 35.6% against the 42.9% previously carried, and we now assume 40.0% (-0.7%p YoY), easing to 38.0% in FY27F and 35.4% in FY28F, with the balance taken back in a provisioning charge of VND11.4tn that holds coverage at 50.9%.</t>
+          <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,570bn (-7.9% YoY) and gross loans to VND640,643bn.
+- NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 54.2%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- FY26F PBT falls to VND7,082bn (-7.2% YoY), 13% below the board-approved plan of VND8,100bn. The opex build is unchanged while total operating income has fallen, so CIR now reads 42.8% against the 40.0% previously targeted.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>6340</v>
+        <v>5514</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>9572</v>
+        <v>6189</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.06748299535065105</v>
+        <v>-0.0716287336606437</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.5097241281408225</v>
+        <v>0.1225130130402452</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>26.451026230697643</v>
+        <v>30.41457845004262</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>17.520436838531054</v>
+        <v>27.09507871776643</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.5308913552671295</v>
+        <v>2.5628476597721668</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.2114406440595267</v>
+        <v>2.341382812783603</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>6340</v>
+        <v>5514</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>9572</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1026,8 +1026,8 @@
         <is>
           <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,570bn (-7.9% YoY) and gross loans to VND640,643bn.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 54.2%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- FY26F PBT falls to VND7,082bn (-7.2% YoY), 13% below the board-approved plan of VND8,100bn. The opex build is unchanged while total operating income has fallen, so CIR now reads 42.8% against the 40.0% previously targeted.</t>
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 55.4%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- We set FY26F PBT at VND7,500bn (-1.7% YoY), 7.4% below the board-approved plan of VND8,100bn, on CIR of 40.0% easing to 38.0% in FY27F and 36.0% in FY28F. On 1H26 opex of VND6,233bn that needs 2H26 costs 4.1% below the first half.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>5514</v>
+        <v>5839</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>6189</v>
+        <v>7765</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>-0.0716287336606437</v>
+        <v>-0.016856226462175772</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.1225130130402452</v>
+        <v>0.329833875663641</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>30.41457845004262</v>
+        <v>28.720133790032538</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>27.09507871776643</v>
+        <v>21.59678311375549</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.5628476597721668</v>
+        <v>2.5501657745228044</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.341382812783603</v>
+        <v>2.2808420803518845</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>5514</v>
+        <v>5839</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>6189</v>
+        <v>7765</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1024,10 +1024,10 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,570bn (-7.9% YoY) and gross loans to VND640,643bn.
+          <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,570bn (-7.9% YoY), then recovers 15.0% in FY27F as NIM turns.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 55.4%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We set FY26F PBT at VND7,500bn (-1.7% YoY), 7.4% below the board-approved plan of VND8,100bn, on CIR of 40.0% easing to 38.0% in FY27F and 36.0% in FY28F. On 1H26 opex of VND6,233bn that needs 2H26 costs 4.1% below the first half.</t>
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 49.8%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- We set FY26F PBT at VND7,500bn (-1.7% YoY), 7.4% below the board-approved plan of VND8,100bn, on CIR of 42.0% easing to 42.0% in FY27F and 42.0% in FY28F, with 2H26 costs +5.6% on the first half.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>5839</v>
+        <v>5840</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>7765</v>
+        <v>8528</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>-0.016856226462175772</v>
+        <v>-0.01677203877819411</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.329833875663641</v>
+        <v>0.46038188201044594</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>28.720133790032538</v>
+        <v>26.45977395324942</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>21.59678311375549</v>
+        <v>18.11839374289098</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.5501657745228044</v>
+        <v>2.349643474650888</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.2808420803518845</v>
+        <v>2.0799144137110366</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>5839</v>
+        <v>5840</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>7765</v>
+        <v>8528</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1024,10 +1024,10 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,570bn (-7.9% YoY), then recovers 15.0% in FY27F as NIM turns.
+          <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,531bn (-8.1% YoY), then recovers 9.9% in FY27F as NIM turns.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 49.8%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We set FY26F PBT at VND7,500bn (-1.7% YoY), 7.4% below the board-approved plan of VND8,100bn, on CIR of 42.0% easing to 42.0% in FY27F and 42.0% in FY28F, with 2H26 costs +5.6% on the first half.</t>
+- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
+- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 43.6% in FY27F and 43.4% in FY28F, with 2H26 costs +5.6% on the first half.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>5840</v>
+        <v>5809</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>8528</v>
+        <v>7507</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>-0.01677203877819411</v>
+        <v>-0.02194116257466805</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.46038188201044594</v>
+        <v>0.2923495386310424</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>26.45977395324942</v>
+        <v>26.599616099710783</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>18.11839374289098</v>
+        <v>20.58236978819768</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.349643474650888</v>
+        <v>2.350744497473714</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.0799144137110366</v>
+        <v>2.109780026216615</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>5840</v>
+        <v>5809</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>8528</v>
+        <v>7507</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1027,7 +1027,7 @@
           <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,531bn (-8.1% YoY), then recovers 9.9% in FY27F as NIM turns.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
 - We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 43.6% in FY27F and 43.4% in FY28F, with 2H26 costs +5.6% on the first half.</t>
+- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, with 2H26 costs +5.6% on the first half.</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1046,25 +1046,25 @@
         <v>5809</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>7507</v>
+        <v>8465</v>
       </c>
       <c r="H6" s="62" t="n">
         <v>-0.02194116257466805</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.2923495386310424</v>
+        <v>0.4572545103980168</v>
       </c>
       <c r="J6" s="63" t="n">
         <v>26.599616099710783</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>20.58236978819768</v>
+        <v>18.25323984925988</v>
       </c>
       <c r="L6" s="63" t="n">
         <v>2.350744497473714</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.109780026216615</v>
+        <v>2.082543959198747</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1610,7 +1610,7 @@
         <v>5809</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>7507</v>
+        <v>8465</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1026,8 +1026,8 @@
         <is>
           <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,531bn (-8.1% YoY), then recovers 9.9% in FY27F as NIM turns.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.5%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND4.0tn charge in 2H26 funds VND11.8tn of write-offs, or 37% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.5%, and it needs 2H26 NPL formation to slow to roughly a quarter of the 1H26 pace.
-- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, with 2H26 costs +5.6% on the first half.</t>
+- We set FY26F NPL at 5.8%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND3.1tn charge in 2H26 funds VND11.0tn of write-offs, or 34% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.8%: on the smaller loan book, 5.5% would have required net NPL recoveries in 2H26 rather than merely slower formation.
+- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, with 2H26 costs +5.6% on the first half. FY27F and FY28F each carry VND1,000bn of specific charge above what write-offs consume, taking PBT to VND9,872bn (+32%) and VND16,271bn (+65%).</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1046,25 +1046,25 @@
         <v>5809</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>8465</v>
+        <v>7686</v>
       </c>
       <c r="H6" s="62" t="n">
         <v>-0.02194116257466805</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.4572545103980168</v>
+        <v>0.3232337143644126</v>
       </c>
       <c r="J6" s="63" t="n">
         <v>26.599616099710783</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>18.25323984925988</v>
+        <v>20.101978819733553</v>
       </c>
       <c r="L6" s="63" t="n">
         <v>2.350744497473714</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.082543959198747</v>
+        <v>2.104627373313192</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1610,7 +1610,7 @@
         <v>5809</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>8465</v>
+        <v>7686</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1027,7 +1027,7 @@
           <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,531bn (-8.1% YoY), then recovers 9.9% in FY27F as NIM turns.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
 - We set FY26F NPL at 5.8%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND3.1tn charge in 2H26 funds VND11.0tn of write-offs, or 34% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.8%: on the smaller loan book, 5.5% would have required net NPL recoveries in 2H26 rather than merely slower formation.
-- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, with 2H26 costs +5.6% on the first half. FY27F and FY28F each carry VND1,000bn of specific charge above what write-offs consume, taking PBT to VND9,872bn (+32%) and VND16,271bn (+65%).</t>
+- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, with 2H26 costs +5.6% on the first half. FY27F and FY28F each carry VND1,000bn of specific charge above what write-offs consume, taking PBT to VND9,872bn (+32%) and VND15,271bn (+55%).</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1049,22 +1049,22 @@
         <v>7686</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>-0.02194116257466805</v>
+        <v>-0.02194423999738493</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.3232337143644126</v>
+        <v>0.32323772213173396</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>26.599616099710783</v>
+        <v>26.599699794594237</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>20.101978819733553</v>
+        <v>20.10198118577073</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.350744497473714</v>
+        <v>2.35074311258121</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.104627373313192</v>
+        <v>2.1046262891651044</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1027,7 +1027,7 @@
           <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,531bn (-8.1% YoY), then recovers 9.9% in FY27F as NIM turns.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
 - We set FY26F NPL at 5.8%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND3.1tn charge in 2H26 funds VND11.0tn of write-offs, or 34% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.8%: on the smaller loan book, 5.5% would have required net NPL recoveries in 2H26 rather than merely slower formation.
-- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, with 2H26 costs +5.6% on the first half. FY27F and FY28F each carry VND1,000bn of specific charge above what write-offs consume, taking PBT to VND9,872bn (+32%) and VND15,271bn (+55%).</t>
+- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, with 2H26 costs +5.6% on the first half. FY27F carries VND1,000bn of specific charge above what write-offs consume and FY28F VND2,000bn, taking PBT to VND9,872bn (+32%) and VND15,271bn (+55%).</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1055,16 +1055,16 @@
         <v>0.32323772213173396</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>26.599699794594237</v>
+        <v>24.340934854538258</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>20.10198118577073</v>
+        <v>18.394982585083085</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.35074311258121</v>
+        <v>2.1511252158839103</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>2.1046262891651044</v>
+        <v>1.925907878408741</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1024,10 +1024,10 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">- We cut FY26F loan growth to 2.3% from 11.7%, in line with the 1.5% delivered in 1H26. NII falls to VND24,531bn (-8.1% YoY), then recovers 9.9% in FY27F as NIM turns.
+          <t xml:space="preserve">- We take FY26F loan growth to 8.0% from the 2.3% carried before; 1H26 delivered 1.5%, so the second half has to add 6.4%. NII VND26,084bn (-2.2% YoY), then +16.5% in FY27F as NIM turns.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.8%, from below 4.5%, and FY27F at 4.0% from 3.1%. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND3.1tn charge in 2H26 funds VND11.0tn of write-offs, or 34% of the Group 5 balance, leaving coverage at 50.9%. Holding coverage near 50% is what caps the improvement at 5.8%: on the smaller loan book, 5.5% would have required net NPL recoveries in 2H26 rather than merely slower formation.
-- We set FY26F PBT at VND7,461bn (-2.2% YoY), 7.9% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, with 2H26 costs +5.6% on the first half. FY27F carries VND1,000bn of specific charge above what write-offs consume and FY28F VND2,000bn, taking PBT to VND9,872bn (+32%) and VND15,271bn (+55%).</t>
+- We set FY26F NPL at 5.8%, from below 4.5%, and FY27F at 4.0% from 3.1%. On the bigger book that is VND39,237bn, so the ratio improves through write-offs and the denominator, not cures. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND3.9tn charge in 2H26 funds VND11.6tn of write-offs, or 36% of the Group 5 balance, leaving coverage at 48.6% - down from 50.9% on the 2.3% book, the reserve being sized to fund write-offs while the denominator grows.
+- We set FY26F PBT at VND7,573bn (-0.7% YoY), 6.5% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, held on the bigger revenue base so 2H26 costs run +16.4% on the first half. FY27F carries VND1,000bn of specific charge above what write-offs consume and FY28F VND2,000bn, taking PBT to VND11,417bn (+51%) and VND17,229bn (+51%).</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>5809</v>
+        <v>5896</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>7686</v>
+        <v>8889</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>-0.02194423999738493</v>
+        <v>-0.007200433233931602</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.32323772213173396</v>
+        <v>0.5075995529779695</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>24.340934854538258</v>
+        <v>23.979453995812538</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>18.394982585083085</v>
+        <v>15.905718430630863</v>
       </c>
       <c r="L6" s="63" t="n">
         <v>2.1511252158839103</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>1.925907878408741</v>
+        <v>1.894860068718794</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>5809</v>
+        <v>5896</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>7686</v>
+        <v>8889</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1024,10 +1024,10 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">- We take FY26F loan growth to 8.0% from the 2.3% carried before; 1H26 delivered 1.5%, so the second half has to add 6.4%. NII VND26,084bn (-2.2% YoY), then +16.5% in FY27F as NIM turns.
+          <t xml:space="preserve">- We take FY26F loan growth to 8.0% from the 2.3% carried before; 1H26 delivered 1.5%, so the second half has to add 6.4%. NII VND26,098bn (-2.2% YoY), then +16.5% in FY27F as NIM turns.
 - NIM troughs in FY26F as elevated NPLs freeze accrued interest income while funding costs remain sticky, before recovering in FY27F.
-- We set FY26F NPL at 5.8%, from below 4.5%, and FY27F at 4.0% from 3.1%. On the bigger book that is VND39,237bn, so the ratio improves through write-offs and the denominator, not cures. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND3.9tn charge in 2H26 funds VND11.6tn of write-offs, or 36% of the Group 5 balance, leaving coverage at 48.6% - down from 50.9% on the 2.3% book, the reserve being sized to fund write-offs while the denominator grows.
-- We set FY26F PBT at VND7,573bn (-0.7% YoY), 6.5% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, held on the bigger revenue base so 2H26 costs run +16.4% on the first half. FY27F carries VND1,000bn of specific charge above what write-offs consume and FY28F VND2,000bn, taking PBT to VND11,417bn (+51%) and VND17,229bn (+51%).</t>
+- We set FY26F NPL at 5.8%, from below 4.5%, and FY27F at 4.0% from 3.1%. On the bigger book that is VND39,237bn, so the ratio improves through write-offs and the denominator, not cures. Reserves reached VND27.2tn at end-2Q26 (56.7% coverage) on VND7.1tn of 1H26 charges and almost no write-offs; a further VND3.3tn charge in 2H26 funds VND11.6tn of write-offs, or 36% of the Group 5 balance, leaving coverage at 47.1% - down from 50.9% on the 2.3% book, the reserve being sized to fund write-offs while the denominator grows.
+- We set FY26F PBT at VND8,180bn (+7.2% YoY), -1.0% below the board-approved plan of VND8,100bn, on CIR of 42.1% easing to 40.0% in FY27F and 38.0% in FY28F, held on the bigger revenue base so 2H26 costs run +16.5% on the first half. FY27F carries VND1,000bn of specific charge above what write-offs consume and FY28F VND2,000bn, taking PBT to VND11,433bn (+40%) and VND17,246bn (+51%).</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="F6" s="61" t="n">
-        <v>5896</v>
+        <v>6369</v>
       </c>
       <c r="G6" s="61" t="n">
-        <v>8889</v>
+        <v>8902</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>-0.007200433233931602</v>
+        <v>0.0723711272619243</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.5075995529779695</v>
+        <v>0.3977068667270389</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>23.979453995812538</v>
+        <v>22.940146961141835</v>
       </c>
       <c r="K6" s="63" t="n">
-        <v>15.905718430630863</v>
+        <v>16.41270248235953</v>
       </c>
       <c r="L6" s="63" t="n">
-        <v>2.1511252158839103</v>
+        <v>2.204046258740995</v>
       </c>
       <c r="M6" s="63" t="n">
-        <v>1.894860068718794</v>
+        <v>1.9431081122242788</v>
       </c>
     </row>
     <row r="7" ht="379.2" customFormat="1" customHeight="1" s="39">
@@ -1607,10 +1607,10 @@
         <v>77500</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>5896</v>
+        <v>6369</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>8889</v>
+        <v>8902</v>
       </c>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="1">

--- a/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
+++ b/Stock_Pick_and_Forecast_Aug26_MAS_RS_EN_updated.xlsx
@@ -1049,13 +1049,13 @@
         <v>8902</v>
       </c>
       <c r="H6" s="62" t="n">
-        <v>0.0723711272619243</v>
+        <v>0.07237112726192518</v>
       </c>
       <c r="I6" s="62" t="n">
-        <v>0.3977068667270389</v>
+        <v>0.3977068667270378</v>
       </c>
       <c r="J6" s="63" t="n">
-        <v>22.940146961141835</v>
+        <v>22.940146961141814</v>
       </c>
       <c r="K6" s="63" t="n">
         <v>16.41270248235953</v>
